--- a/data/open-pos.xlsx
+++ b/data/open-pos.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="301">
   <si>
     <t>Account</t>
   </si>
@@ -137,18 +137,6 @@
     <t>5113</t>
   </si>
   <si>
-    <t>PLASTIX PLUS LLC</t>
-  </si>
-  <si>
-    <t>PP-AMK-iS320 Horizontal Bracket f</t>
-  </si>
-  <si>
-    <t>PP-AMK-iC700 Horizontal Bracket f</t>
-  </si>
-  <si>
-    <t>Horizontal mounting bracket for i</t>
-  </si>
-  <si>
     <t>AED123 LLC</t>
   </si>
   <si>
@@ -167,6 +155,27 @@
     <t>SHIPPING</t>
   </si>
   <si>
+    <t>STASH ENTERPRISES LLC</t>
+  </si>
+  <si>
+    <t>Firecom Digital Intercom</t>
+  </si>
+  <si>
+    <t>Firecom Wireless Base</t>
+  </si>
+  <si>
+    <t>Firecom Wireless Headset w/coiled</t>
+  </si>
+  <si>
+    <t>NFPA Hanger</t>
+  </si>
+  <si>
+    <t>Motorola Radio Interface Cable</t>
+  </si>
+  <si>
+    <t>install 5 position system</t>
+  </si>
+  <si>
     <t>100-30-340-5115-</t>
   </si>
   <si>
@@ -185,6 +194,27 @@
     <t>Fuel Station 211</t>
   </si>
   <si>
+    <t>100-30-340-5201-</t>
+  </si>
+  <si>
+    <t>Maint - Buildings/Facilities</t>
+  </si>
+  <si>
+    <t>5201</t>
+  </si>
+  <si>
+    <t>BAR NONE COATINGS LLC</t>
+  </si>
+  <si>
+    <t>PREMIUM FLAKE FLOORING W/HIGH WEA</t>
+  </si>
+  <si>
+    <t>LANE CONCRETE &amp; EXCAVATION LL</t>
+  </si>
+  <si>
+    <t>Remove &amp; Replace 1904sqft of exis</t>
+  </si>
+  <si>
     <t>100-30-340-5204-</t>
   </si>
   <si>
@@ -200,24 +230,6 @@
     <t>FY26 VEHICLE MAINTENANCE  HGAC FS</t>
   </si>
   <si>
-    <t>100-30-340-5352-</t>
-  </si>
-  <si>
-    <t>Printing Services</t>
-  </si>
-  <si>
-    <t>5352</t>
-  </si>
-  <si>
-    <t>GUEST COMMUNICATIONS CORPORAT</t>
-  </si>
-  <si>
-    <t>Emergency Guidebook Directories</t>
-  </si>
-  <si>
-    <t>Wall Mounting Hooks</t>
-  </si>
-  <si>
     <t>100-30-340-5374-</t>
   </si>
   <si>
@@ -266,6 +278,12 @@
     <t>Bunker Gear Cleaning &amp; Inspection</t>
   </si>
   <si>
+    <t>TENSOR MEDICAL SYSTEMS INC</t>
+  </si>
+  <si>
+    <t>Tensor Analytics Platform Subscri</t>
+  </si>
+  <si>
     <t>100-30-340-5613-</t>
   </si>
   <si>
@@ -293,135 +311,114 @@
     <t>PPE- COATS, PANTS, HELMETS, BOOTS</t>
   </si>
   <si>
+    <t>LIGHTHOUSE UNIFORMS INC</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS CAP-CAPTAIN Name: W</t>
+  </si>
+  <si>
+    <t>CLASS A CAP DEVICE Name: Wes Vaug</t>
+  </si>
+  <si>
+    <t>CLASS A BELT &amp; BUCKLE Name: Wes V</t>
+  </si>
+  <si>
+    <t>CLASS A BELT &amp; BUCKLE Name: Curti</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS SHIRT Name: Chris H</t>
+  </si>
+  <si>
+    <t>SHOES Name: Wes Vaughn Shoe Style</t>
+  </si>
+  <si>
+    <t>SHOES Name: Curtis Greenburg Shoe</t>
+  </si>
+  <si>
+    <t>SHOES Name: Jacob Wasinger Shoe S</t>
+  </si>
+  <si>
+    <t>SHOES Name: Chris Holcomb Shoe St</t>
+  </si>
+  <si>
+    <t>SHOES Name: Sharrod Murray Shoe S</t>
+  </si>
+  <si>
+    <t>SHOES Name: Matt Baker Shoe Style</t>
+  </si>
+  <si>
+    <t>TIE/ASCOTS Name: Matt Baker Tie C</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS UNIFORM OSCAR VAZQU</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS SHIRT Name: Oscar V</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS PANTS &amp; SKIRTS Name</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS JACKET KAMERON EBAN</t>
+  </si>
+  <si>
+    <t>CLASS A BELT &amp; BUCKLE Name: Kamer</t>
+  </si>
+  <si>
+    <t>SHOES Name: Kameron Ebanks Shoe S</t>
+  </si>
+  <si>
+    <t>CLASS A DRESS CAP Name: Kameron E</t>
+  </si>
+  <si>
+    <t>CLASS A CAP DEVICE Name: Kameron</t>
+  </si>
+  <si>
+    <t>CLASS A BELT &amp; BUCKLE Name: Micha</t>
+  </si>
+  <si>
+    <t>HANDLING</t>
+  </si>
+  <si>
+    <t>EXPEDITE FEES</t>
+  </si>
+  <si>
     <t>NAFECO, INC.</t>
   </si>
   <si>
-    <t>Phenix TL2 Leather Helmet. Bend o</t>
-  </si>
-  <si>
-    <t>Flip Down Eye Shield (Bourkes)</t>
+    <t>Phenix TL2 Leather Helmet. White</t>
+  </si>
+  <si>
+    <t>Phenix TL2 Leather Helmet. Red (0</t>
+  </si>
+  <si>
+    <t>Phenix TL2 Leather Helmet. Yellow</t>
+  </si>
+  <si>
+    <t>Phenix TL2 Leather Helmet. Black</t>
+  </si>
+  <si>
+    <t>Flip Down Eye Shield (Bourkes) Ca</t>
+  </si>
+  <si>
+    <t>Paul Conway 6" WB Shield Center N</t>
+  </si>
+  <si>
+    <t>ESTIMATED FREIGHT</t>
+  </si>
+  <si>
+    <t>RAGTOP FIRE HELMETS AND RESTO</t>
   </si>
   <si>
     <t>FREIGHT</t>
   </si>
   <si>
-    <t>LIGHTHOUSE UNIFORMS INC</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS CAP-CAPTAIN Name: W</t>
-  </si>
-  <si>
-    <t>CLASS A CAP DEVICE Name: Wes Vaug</t>
-  </si>
-  <si>
-    <t>CLASS A BELT &amp; BUCKLE Name: Wes V</t>
-  </si>
-  <si>
-    <t>CLASS A BELT &amp; BUCKLE Name: Curti</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS SHIRT Name: Chris H</t>
-  </si>
-  <si>
-    <t>SHOES Name: Wes Vaughn Shoe Style</t>
-  </si>
-  <si>
-    <t>SHOES Name: Curtis Greenburg Shoe</t>
-  </si>
-  <si>
-    <t>SHOES Name: Jacob Wasinger Shoe S</t>
-  </si>
-  <si>
-    <t>SHOES Name: Chris Holcomb Shoe St</t>
-  </si>
-  <si>
-    <t>SHOES Name: Sharrod Murray Shoe S</t>
-  </si>
-  <si>
-    <t>SHOES Name: Matt Baker Shoe Style</t>
-  </si>
-  <si>
-    <t>TIE/ASCOTS Name: Matt Baker Tie C</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS UNIFORM OSCAR VAZQU</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS SHIRT Name: Oscar V</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS PANTS &amp; SKIRTS Name</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS JACKET KAMERON EBAN</t>
-  </si>
-  <si>
-    <t>CLASS A BELT &amp; BUCKLE Name: Kamer</t>
-  </si>
-  <si>
-    <t>SHOES Name: Kameron Ebanks Shoe S</t>
-  </si>
-  <si>
-    <t>CLASS A DRESS CAP Name: Kameron E</t>
-  </si>
-  <si>
-    <t>CLASS A CAP DEVICE Name: Kameron</t>
-  </si>
-  <si>
-    <t>CLASS A BELT &amp; BUCKLE Name: Micha</t>
-  </si>
-  <si>
-    <t>HANDLING</t>
-  </si>
-  <si>
-    <t>EXPEDITE FEES</t>
-  </si>
-  <si>
-    <t>Phenix TL2 Leather Helmet. White</t>
-  </si>
-  <si>
-    <t>Phenix TL2 Leather Helmet. Red (0</t>
-  </si>
-  <si>
-    <t>Phenix TL2 Leather Helmet. Yellow</t>
-  </si>
-  <si>
-    <t>Phenix TL2 Leather Helmet. Black</t>
-  </si>
-  <si>
-    <t>Flip Down Eye Shield (Bourkes) Ca</t>
-  </si>
-  <si>
-    <t>Paul Conway 6" WB Shield Center N</t>
-  </si>
-  <si>
-    <t>ESTIMATED FREIGHT</t>
-  </si>
-  <si>
-    <t>RAGTOP FIRE HELMETS AND RESTO</t>
-  </si>
-  <si>
-    <t>SMALL</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>LARGE</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>100-30-350-5352-</t>
+    <t>100-30-350-5374-</t>
   </si>
   <si>
     <t>100350</t>
   </si>
   <si>
-    <t>100-30-350-5374-</t>
-  </si>
-  <si>
     <t>CITY OF DUNCANVILLE</t>
   </si>
   <si>
@@ -476,15 +473,9 @@
     <t>221-30-380-5201-</t>
   </si>
   <si>
-    <t>Maint - Buildings/Facilities</t>
-  </si>
-  <si>
     <t>221380</t>
   </si>
   <si>
-    <t>5201</t>
-  </si>
-  <si>
     <t>221</t>
   </si>
   <si>
@@ -545,18 +536,6 @@
     <t>Central Athletic District (Blanke</t>
   </si>
   <si>
-    <t>100-40-410-5208-</t>
-  </si>
-  <si>
-    <t>Maint - Landscaping/Fencing</t>
-  </si>
-  <si>
-    <t>5208</t>
-  </si>
-  <si>
-    <t>Live Oaks &amp; Wildflowers (Blanket)</t>
-  </si>
-  <si>
     <t>100-40-430-5374-</t>
   </si>
   <si>
@@ -713,6 +692,15 @@
     <t>Hoopla Digital E-books, movies, m</t>
   </si>
   <si>
+    <t>MISSION TELECOM</t>
+  </si>
+  <si>
+    <t>Franklin T10 Mobile Hotspot</t>
+  </si>
+  <si>
+    <t>Power Unlimited Hotspot Date of S</t>
+  </si>
+  <si>
     <t>100-40-450-5201-</t>
   </si>
   <si>
@@ -737,18 +725,6 @@
     <t>Annual Panic Button Monitoring: S</t>
   </si>
   <si>
-    <t>SOUTHLAND INDUSTRIES</t>
-  </si>
-  <si>
-    <t>5 hours Labor - HVAC Repair AAON</t>
-  </si>
-  <si>
-    <t>(4) Crank Case Heaters</t>
-  </si>
-  <si>
-    <t>Service Vehicle Fee</t>
-  </si>
-  <si>
     <t>100-40-450-5374-</t>
   </si>
   <si>
@@ -812,6 +788,12 @@
     <t>611</t>
   </si>
   <si>
+    <t>TEXAS DEPARTMENT OF TRANSPORT</t>
+  </si>
+  <si>
+    <t>Texas Highways October 2025 1/2 p</t>
+  </si>
+  <si>
     <t>CLEAR CHANNEL OUTDOOR, INC.</t>
   </si>
   <si>
@@ -824,10 +806,10 @@
     <t>261-60-611-5374-</t>
   </si>
   <si>
-    <t>MCWEENEY, ARIANA</t>
-  </si>
-  <si>
-    <t>Upfront mural design fee for poss</t>
+    <t>GRANICUS, LLC</t>
+  </si>
+  <si>
+    <t>Website Consulting</t>
   </si>
   <si>
     <t>SUPERSTAR COLLISION LLC</t>
@@ -872,21 +854,6 @@
     <t>Additional funds are needed to pu</t>
   </si>
   <si>
-    <t>100-70-710-5216-</t>
-  </si>
-  <si>
-    <t>Maint - Signs &amp; Signals</t>
-  </si>
-  <si>
-    <t>5216</t>
-  </si>
-  <si>
-    <t>DURABLE SPECIALTIES INC.</t>
-  </si>
-  <si>
-    <t>EMERGENCY PO - Installation of a</t>
-  </si>
-  <si>
     <t>100-70-710-5374-</t>
   </si>
   <si>
@@ -950,40 +917,7 @@
     <t>CONSOLIDATED TRAFFIC CONTROLS</t>
   </si>
   <si>
-    <t>Guardian Board with Complete 3 Wa</t>
-  </si>
-  <si>
     <t>105 Amp 12V Batteries for solar l</t>
-  </si>
-  <si>
-    <t>100-70-710-5504-</t>
-  </si>
-  <si>
-    <t>Street Lighting</t>
-  </si>
-  <si>
-    <t>5504</t>
-  </si>
-  <si>
-    <t>TEXAS DEPT. OF TRANSPORTATION</t>
-  </si>
-  <si>
-    <t>FY26 Q4 FM 1382 Lighting Maintena</t>
-  </si>
-  <si>
-    <t>100-70-710-5802-</t>
-  </si>
-  <si>
-    <t>Equipment Lease Finance only</t>
-  </si>
-  <si>
-    <t>5802</t>
-  </si>
-  <si>
-    <t>UNDERWOOD EQUIPMENT</t>
-  </si>
-  <si>
-    <t>CAT 963D Track Loader (Weekly Ren</t>
   </si>
 </sst>
 </file>
@@ -1470,12 +1404,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872fe8e1-9d70-4c93-aebf-c24cfe41d0fe}">
-  <dimension ref="A1:Q161"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{c3892fe6-d321-4778-b3ed-a2e857441bf1}">
+  <dimension ref="A1:Q151"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="15.5714285714286" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.7142857142857" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23" style="3" customWidth="1"/>
     <col min="3" max="3" width="8.57142857142857" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.8571428571429" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.2857142857143" style="3" customWidth="1"/>
@@ -1486,11 +1420,11 @@
     <col min="10" max="10" width="13.7142857142857" style="3" customWidth="1"/>
     <col min="11" max="11" width="11.5714285714286" style="5" customWidth="1"/>
     <col min="12" max="12" width="14.1428571428571" style="5" customWidth="1"/>
-    <col min="13" max="13" width="30.4285714285714" style="3" customWidth="1"/>
+    <col min="13" max="13" width="29.7142857142857" style="3" customWidth="1"/>
     <col min="14" max="14" width="10.7142857142857" style="7" customWidth="1"/>
     <col min="15" max="15" width="14.8571428571429" style="9" customWidth="1"/>
     <col min="16" max="16" width="12.4285714285714" style="9" customWidth="1"/>
-    <col min="17" max="17" width="31.8571428571429" style="3" customWidth="1"/>
+    <col min="17" max="17" width="33.1428571428571" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12.75">
@@ -1593,7 +1527,7 @@
         <v>100000</v>
       </c>
       <c r="P2" s="9">
-        <v>36281.74</v>
+        <v>28627.91</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>27</v>
@@ -2099,7 +2033,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="5">
-        <v>2620351</v>
+        <v>2620404</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>24</v>
@@ -2111,19 +2045,19 @@
         <v>1</v>
       </c>
       <c r="L12" s="5">
-        <v>5115</v>
+        <v>5113</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>40</v>
       </c>
       <c r="N12" s="7">
-        <v>46076</v>
+        <v>46121</v>
       </c>
       <c r="O12" s="9">
-        <v>1180</v>
+        <v>9600</v>
       </c>
       <c r="P12" s="9">
-        <v>1180</v>
+        <v>1600</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>41</v>
@@ -2152,7 +2086,7 @@
         <v>23</v>
       </c>
       <c r="H13" s="5">
-        <v>2620351</v>
+        <v>2620485</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>24</v>
@@ -2161,25 +2095,25 @@
         <v>25</v>
       </c>
       <c r="K13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>5115</v>
+        <v>1428</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N13" s="7">
-        <v>46076</v>
+        <v>46217</v>
       </c>
       <c r="O13" s="9">
-        <v>1120</v>
+        <v>2696</v>
       </c>
       <c r="P13" s="9">
-        <v>1120</v>
+        <v>2696</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="12.75">
@@ -2205,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="H14" s="5">
-        <v>2620351</v>
+        <v>2620485</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>24</v>
@@ -2214,25 +2148,25 @@
         <v>25</v>
       </c>
       <c r="K14" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="5">
-        <v>5115</v>
+        <v>1428</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N14" s="7">
-        <v>46076</v>
+        <v>46217</v>
       </c>
       <c r="O14" s="9">
-        <v>1120</v>
+        <v>940</v>
       </c>
       <c r="P14" s="9">
-        <v>1120</v>
+        <v>940</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="12.75">
@@ -2258,7 +2192,7 @@
         <v>23</v>
       </c>
       <c r="H15" s="5">
-        <v>2620404</v>
+        <v>2620485</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>24</v>
@@ -2267,22 +2201,22 @@
         <v>25</v>
       </c>
       <c r="K15" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5">
-        <v>5113</v>
+        <v>1428</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N15" s="7">
-        <v>46121</v>
+        <v>46217</v>
       </c>
       <c r="O15" s="9">
-        <v>9600</v>
+        <v>85</v>
       </c>
       <c r="P15" s="9">
-        <v>3200</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>45</v>
@@ -2311,7 +2245,7 @@
         <v>23</v>
       </c>
       <c r="H16" s="5">
-        <v>2620485</v>
+        <v>2620504</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>24</v>
@@ -2323,19 +2257,19 @@
         <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>1428</v>
+        <v>5218</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N16" s="7">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="O16" s="9">
-        <v>2696</v>
+        <v>1067.63</v>
       </c>
       <c r="P16" s="9">
-        <v>2696</v>
+        <v>1067.63</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>47</v>
@@ -2364,7 +2298,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="5">
-        <v>2620485</v>
+        <v>2620504</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>24</v>
@@ -2376,19 +2310,19 @@
         <v>2</v>
       </c>
       <c r="L17" s="5">
-        <v>1428</v>
+        <v>5218</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N17" s="7">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="O17" s="9">
-        <v>940</v>
+        <v>1360.13</v>
       </c>
       <c r="P17" s="9">
-        <v>940</v>
+        <v>1360.13</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>48</v>
@@ -2417,7 +2351,7 @@
         <v>23</v>
       </c>
       <c r="H18" s="5">
-        <v>2620485</v>
+        <v>2620504</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>24</v>
@@ -2429,19 +2363,19 @@
         <v>3</v>
       </c>
       <c r="L18" s="5">
-        <v>1428</v>
+        <v>5218</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N18" s="7">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="O18" s="9">
-        <v>85</v>
+        <v>4606.90</v>
       </c>
       <c r="P18" s="9">
-        <v>85</v>
+        <v>4606.90</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>49</v>
@@ -2449,16 +2383,16 @@
     </row>
     <row r="19" spans="1:17" ht="12.75">
       <c r="A19" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>21</v>
@@ -2470,7 +2404,7 @@
         <v>23</v>
       </c>
       <c r="H19" s="5">
-        <v>2620157</v>
+        <v>2620504</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>24</v>
@@ -2479,39 +2413,39 @@
         <v>25</v>
       </c>
       <c r="K19" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L19" s="5">
-        <v>3972</v>
+        <v>5218</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N19" s="7">
-        <v>45951</v>
+        <v>46233</v>
       </c>
       <c r="O19" s="9">
-        <v>50000</v>
+        <v>73.15</v>
       </c>
       <c r="P19" s="9">
-        <v>18025.90</v>
+        <v>73.15</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="12.75">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>21</v>
@@ -2523,7 +2457,7 @@
         <v>23</v>
       </c>
       <c r="H20" s="5">
-        <v>2620429</v>
+        <v>2620504</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>24</v>
@@ -2532,39 +2466,39 @@
         <v>25</v>
       </c>
       <c r="K20" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5">
-        <v>3972</v>
+        <v>5218</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N20" s="7">
-        <v>46149</v>
+        <v>46233</v>
       </c>
       <c r="O20" s="9">
-        <v>15000</v>
+        <v>277.88</v>
       </c>
       <c r="P20" s="9">
-        <v>4070.74</v>
+        <v>277.88</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="12.75">
       <c r="A21" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>21</v>
@@ -2576,7 +2510,7 @@
         <v>23</v>
       </c>
       <c r="H21" s="5">
-        <v>2620179</v>
+        <v>2620504</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>24</v>
@@ -2585,39 +2519,39 @@
         <v>25</v>
       </c>
       <c r="K21" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L21" s="5">
-        <v>1661</v>
+        <v>5218</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="N21" s="7">
-        <v>45964</v>
+        <v>46233</v>
       </c>
       <c r="O21" s="9">
-        <v>186000</v>
+        <v>682.50</v>
       </c>
       <c r="P21" s="9">
-        <v>127566.48</v>
+        <v>682.50</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="12.75">
       <c r="A22" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
@@ -2629,7 +2563,7 @@
         <v>23</v>
       </c>
       <c r="H22" s="5">
-        <v>2620458</v>
+        <v>2620157</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>24</v>
@@ -2641,36 +2575,36 @@
         <v>1</v>
       </c>
       <c r="L22" s="5">
-        <v>5187</v>
+        <v>3972</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="N22" s="7">
-        <v>46184</v>
+        <v>45951</v>
       </c>
       <c r="O22" s="9">
-        <v>2827</v>
+        <v>50000</v>
       </c>
       <c r="P22" s="9">
-        <v>2827</v>
+        <v>13997.07</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="12.75">
       <c r="A23" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>21</v>
@@ -2682,7 +2616,7 @@
         <v>23</v>
       </c>
       <c r="H23" s="5">
-        <v>2620458</v>
+        <v>2620429</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>24</v>
@@ -2691,39 +2625,39 @@
         <v>25</v>
       </c>
       <c r="K23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
-        <v>5187</v>
+        <v>3972</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="N23" s="7">
-        <v>46184</v>
+        <v>46149</v>
       </c>
       <c r="O23" s="9">
-        <v>56.25</v>
+        <v>15000</v>
       </c>
       <c r="P23" s="9">
-        <v>56.25</v>
+        <v>688.05</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="12.75">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>21</v>
@@ -2735,7 +2669,7 @@
         <v>23</v>
       </c>
       <c r="H24" s="5">
-        <v>2620218</v>
+        <v>2620514</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>24</v>
@@ -2747,36 +2681,36 @@
         <v>1</v>
       </c>
       <c r="L24" s="5">
-        <v>4881</v>
+        <v>5231</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="N24" s="7">
-        <v>45981</v>
+        <v>46244</v>
       </c>
       <c r="O24" s="9">
-        <v>72150</v>
+        <v>32300</v>
       </c>
       <c r="P24" s="9">
-        <v>4625</v>
+        <v>32300</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="12.75">
       <c r="A25" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>21</v>
@@ -2788,7 +2722,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="5">
-        <v>2620218</v>
+        <v>2620518</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>24</v>
@@ -2797,39 +2731,39 @@
         <v>25</v>
       </c>
       <c r="K25" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="5">
-        <v>4881</v>
+        <v>5233</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N25" s="7">
-        <v>45981</v>
+        <v>46247</v>
       </c>
       <c r="O25" s="9">
-        <v>3000</v>
+        <v>35080</v>
       </c>
       <c r="P25" s="9">
-        <v>3000</v>
+        <v>35080</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="12.75">
       <c r="A26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>21</v>
@@ -2841,7 +2775,7 @@
         <v>23</v>
       </c>
       <c r="H26" s="5">
-        <v>2620309</v>
+        <v>2620179</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>24</v>
@@ -2853,36 +2787,36 @@
         <v>1</v>
       </c>
       <c r="L26" s="5">
-        <v>1012</v>
+        <v>1661</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N26" s="7">
-        <v>46043</v>
+        <v>45964</v>
       </c>
       <c r="O26" s="9">
-        <v>20819.66</v>
+        <v>186000</v>
       </c>
       <c r="P26" s="9">
-        <v>3036.44</v>
+        <v>121653.02</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="12.75">
       <c r="A27" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>21</v>
@@ -2894,7 +2828,7 @@
         <v>23</v>
       </c>
       <c r="H27" s="5">
-        <v>2620309</v>
+        <v>2620218</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>24</v>
@@ -2903,22 +2837,22 @@
         <v>25</v>
       </c>
       <c r="K27" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="5">
-        <v>1012</v>
+        <v>4881</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N27" s="7">
-        <v>46043</v>
+        <v>45981</v>
       </c>
       <c r="O27" s="9">
-        <v>2633.96</v>
+        <v>72150</v>
       </c>
       <c r="P27" s="9">
-        <v>658.49</v>
+        <v>4625</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>75</v>
@@ -2926,16 +2860,16 @@
     </row>
     <row r="28" spans="1:17" ht="12.75">
       <c r="A28" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>21</v>
@@ -2947,7 +2881,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="5">
-        <v>2620309</v>
+        <v>2620218</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>24</v>
@@ -2956,22 +2890,22 @@
         <v>25</v>
       </c>
       <c r="K28" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5">
-        <v>1012</v>
+        <v>4881</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N28" s="7">
-        <v>46043</v>
+        <v>45981</v>
       </c>
       <c r="O28" s="9">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="P28" s="9">
-        <v>62.50</v>
+        <v>3000</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>76</v>
@@ -2979,16 +2913,16 @@
     </row>
     <row r="29" spans="1:17" ht="12.75">
       <c r="A29" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>21</v>
@@ -3009,39 +2943,39 @@
         <v>25</v>
       </c>
       <c r="K29" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L29" s="5">
         <v>1012</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N29" s="7">
         <v>46043</v>
       </c>
       <c r="O29" s="9">
-        <v>734.24</v>
+        <v>20819.66</v>
       </c>
       <c r="P29" s="9">
-        <v>183.56</v>
+        <v>3036.44</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="12.75">
       <c r="A30" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>21</v>
@@ -3062,39 +2996,39 @@
         <v>25</v>
       </c>
       <c r="K30" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L30" s="5">
         <v>1012</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N30" s="7">
         <v>46043</v>
       </c>
       <c r="O30" s="9">
-        <v>32.98</v>
+        <v>2633.96</v>
       </c>
       <c r="P30" s="9">
-        <v>8.33</v>
+        <v>658.49</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="12.75">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>21</v>
@@ -3115,39 +3049,39 @@
         <v>25</v>
       </c>
       <c r="K31" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5">
         <v>1012</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N31" s="7">
         <v>46043</v>
       </c>
       <c r="O31" s="9">
-        <v>14.40</v>
+        <v>250</v>
       </c>
       <c r="P31" s="9">
-        <v>3.54</v>
+        <v>62.50</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="12.75">
       <c r="A32" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>21</v>
@@ -3168,39 +3102,39 @@
         <v>25</v>
       </c>
       <c r="K32" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5">
         <v>1012</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N32" s="7">
         <v>46043</v>
       </c>
       <c r="O32" s="9">
-        <v>15.04</v>
+        <v>734.24</v>
       </c>
       <c r="P32" s="9">
-        <v>3.76</v>
+        <v>183.56</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="12.75">
       <c r="A33" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>21</v>
@@ -3212,7 +3146,7 @@
         <v>23</v>
       </c>
       <c r="H33" s="5">
-        <v>2620385</v>
+        <v>2620309</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>24</v>
@@ -3221,22 +3155,22 @@
         <v>25</v>
       </c>
       <c r="K33" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" s="5">
-        <v>4757</v>
+        <v>1012</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N33" s="7">
-        <v>46104</v>
+        <v>46043</v>
       </c>
       <c r="O33" s="9">
-        <v>20000</v>
+        <v>32.98</v>
       </c>
       <c r="P33" s="9">
-        <v>446.13</v>
+        <v>8.33</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>82</v>
@@ -3244,16 +3178,16 @@
     </row>
     <row r="34" spans="1:17" ht="12.75">
       <c r="A34" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>21</v>
@@ -3265,7 +3199,7 @@
         <v>23</v>
       </c>
       <c r="H34" s="5">
-        <v>2620391</v>
+        <v>2620309</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>24</v>
@@ -3274,39 +3208,39 @@
         <v>25</v>
       </c>
       <c r="K34" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L34" s="5">
-        <v>1212</v>
+        <v>1012</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N34" s="7">
-        <v>46111</v>
+        <v>46043</v>
       </c>
       <c r="O34" s="9">
-        <v>3000</v>
+        <v>14.40</v>
       </c>
       <c r="P34" s="9">
-        <v>3000</v>
+        <v>3.54</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75">
       <c r="A35" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>21</v>
@@ -3318,7 +3252,7 @@
         <v>23</v>
       </c>
       <c r="H35" s="5">
-        <v>2620155</v>
+        <v>2620309</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>24</v>
@@ -3327,39 +3261,39 @@
         <v>25</v>
       </c>
       <c r="K35" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L35" s="5">
-        <v>1056</v>
+        <v>1012</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="N35" s="7">
-        <v>45951</v>
+        <v>46043</v>
       </c>
       <c r="O35" s="9">
-        <v>65000</v>
+        <v>15.04</v>
       </c>
       <c r="P35" s="9">
-        <v>3432.94</v>
+        <v>3.76</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.75">
       <c r="A36" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>21</v>
@@ -3371,7 +3305,7 @@
         <v>23</v>
       </c>
       <c r="H36" s="5">
-        <v>2620418</v>
+        <v>2620385</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>24</v>
@@ -3383,36 +3317,36 @@
         <v>1</v>
       </c>
       <c r="L36" s="5">
-        <v>1158</v>
+        <v>4757</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N36" s="7">
-        <v>46142</v>
+        <v>46104</v>
       </c>
       <c r="O36" s="9">
-        <v>6862.80</v>
+        <v>20000</v>
       </c>
       <c r="P36" s="9">
-        <v>6862.80</v>
+        <v>446.13</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75">
       <c r="A37" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>21</v>
@@ -3424,7 +3358,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="5">
-        <v>2620418</v>
+        <v>2620505</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>24</v>
@@ -3436,36 +3370,36 @@
         <v>2</v>
       </c>
       <c r="L37" s="5">
-        <v>1158</v>
+        <v>5220</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N37" s="7">
-        <v>46142</v>
+        <v>46233</v>
       </c>
       <c r="O37" s="9">
-        <v>385.20</v>
+        <v>7300</v>
       </c>
       <c r="P37" s="9">
-        <v>385.20</v>
+        <v>4800</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="12.75">
       <c r="A38" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>21</v>
@@ -3477,7 +3411,7 @@
         <v>23</v>
       </c>
       <c r="H38" s="5">
-        <v>2620418</v>
+        <v>2620391</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>24</v>
@@ -3486,39 +3420,39 @@
         <v>25</v>
       </c>
       <c r="K38" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="5">
-        <v>1158</v>
+        <v>1212</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>92</v>
       </c>
       <c r="N38" s="7">
-        <v>46142</v>
+        <v>46111</v>
       </c>
       <c r="O38" s="9">
-        <v>125</v>
+        <v>3000</v>
       </c>
       <c r="P38" s="9">
-        <v>96.50</v>
+        <v>3000</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="12.75">
       <c r="A39" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>21</v>
@@ -3530,7 +3464,7 @@
         <v>23</v>
       </c>
       <c r="H39" s="5">
-        <v>2620482</v>
+        <v>2620155</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>24</v>
@@ -3542,19 +3476,19 @@
         <v>1</v>
       </c>
       <c r="L39" s="5">
-        <v>5194</v>
+        <v>1056</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>96</v>
       </c>
       <c r="N39" s="7">
-        <v>46210</v>
+        <v>45951</v>
       </c>
       <c r="O39" s="9">
-        <v>74.95</v>
+        <v>65000</v>
       </c>
       <c r="P39" s="9">
-        <v>74.95</v>
+        <v>2483.34</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>97</v>
@@ -3562,16 +3496,16 @@
     </row>
     <row r="40" spans="1:17" ht="12.75">
       <c r="A40" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>21</v>
@@ -3592,39 +3526,39 @@
         <v>25</v>
       </c>
       <c r="K40" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="5">
         <v>5194</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N40" s="7">
         <v>46210</v>
       </c>
       <c r="O40" s="9">
-        <v>29.95</v>
+        <v>74.95</v>
       </c>
       <c r="P40" s="9">
-        <v>29.95</v>
+        <v>74.95</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="12.75">
       <c r="A41" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>21</v>
@@ -3645,39 +3579,39 @@
         <v>25</v>
       </c>
       <c r="K41" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L41" s="5">
         <v>5194</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N41" s="7">
         <v>46210</v>
       </c>
       <c r="O41" s="9">
-        <v>24.95</v>
+        <v>29.95</v>
       </c>
       <c r="P41" s="9">
-        <v>24.95</v>
+        <v>29.95</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="12.75">
       <c r="A42" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>21</v>
@@ -3698,13 +3632,13 @@
         <v>25</v>
       </c>
       <c r="K42" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" s="5">
         <v>5194</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N42" s="7">
         <v>46210</v>
@@ -3716,21 +3650,21 @@
         <v>24.95</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="12.75">
       <c r="A43" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>21</v>
@@ -3751,39 +3685,39 @@
         <v>25</v>
       </c>
       <c r="K43" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L43" s="5">
         <v>5194</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N43" s="7">
         <v>46210</v>
       </c>
       <c r="O43" s="9">
-        <v>67.76</v>
+        <v>24.95</v>
       </c>
       <c r="P43" s="9">
-        <v>67.76</v>
+        <v>24.95</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="12.75">
       <c r="A44" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>21</v>
@@ -3804,39 +3738,39 @@
         <v>25</v>
       </c>
       <c r="K44" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L44" s="5">
         <v>5194</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N44" s="7">
         <v>46210</v>
       </c>
       <c r="O44" s="9">
-        <v>99.95</v>
+        <v>67.76</v>
       </c>
       <c r="P44" s="9">
-        <v>99.95</v>
+        <v>67.76</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="12.75">
       <c r="A45" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>21</v>
@@ -3857,13 +3791,13 @@
         <v>25</v>
       </c>
       <c r="K45" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45" s="5">
         <v>5194</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N45" s="7">
         <v>46210</v>
@@ -3875,21 +3809,21 @@
         <v>99.95</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="12.75">
       <c r="A46" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>21</v>
@@ -3910,13 +3844,13 @@
         <v>25</v>
       </c>
       <c r="K46" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L46" s="5">
         <v>5194</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N46" s="7">
         <v>46210</v>
@@ -3928,21 +3862,21 @@
         <v>99.95</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="12.75">
       <c r="A47" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>21</v>
@@ -3963,13 +3897,13 @@
         <v>25</v>
       </c>
       <c r="K47" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L47" s="5">
         <v>5194</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N47" s="7">
         <v>46210</v>
@@ -3981,21 +3915,21 @@
         <v>99.95</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="12.75">
       <c r="A48" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>21</v>
@@ -4016,13 +3950,13 @@
         <v>25</v>
       </c>
       <c r="K48" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L48" s="5">
         <v>5194</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N48" s="7">
         <v>46210</v>
@@ -4034,21 +3968,21 @@
         <v>99.95</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="12.75">
       <c r="A49" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>21</v>
@@ -4069,13 +4003,13 @@
         <v>25</v>
       </c>
       <c r="K49" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L49" s="5">
         <v>5194</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N49" s="7">
         <v>46210</v>
@@ -4087,21 +4021,21 @@
         <v>99.95</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="12.75">
       <c r="A50" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>21</v>
@@ -4122,39 +4056,39 @@
         <v>25</v>
       </c>
       <c r="K50" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L50" s="5">
         <v>5194</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N50" s="7">
         <v>46210</v>
       </c>
       <c r="O50" s="9">
-        <v>11.95</v>
+        <v>99.95</v>
       </c>
       <c r="P50" s="9">
-        <v>11.95</v>
+        <v>99.95</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="12.75">
       <c r="A51" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>21</v>
@@ -4175,39 +4109,39 @@
         <v>25</v>
       </c>
       <c r="K51" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L51" s="5">
         <v>5194</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N51" s="7">
         <v>46210</v>
       </c>
       <c r="O51" s="9">
-        <v>511.30</v>
+        <v>11.95</v>
       </c>
       <c r="P51" s="9">
-        <v>511.30</v>
+        <v>11.95</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="12.75">
       <c r="A52" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>21</v>
@@ -4228,39 +4162,39 @@
         <v>25</v>
       </c>
       <c r="K52" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L52" s="5">
         <v>5194</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N52" s="7">
         <v>46210</v>
       </c>
       <c r="O52" s="9">
-        <v>74.71</v>
+        <v>511.30</v>
       </c>
       <c r="P52" s="9">
-        <v>74.71</v>
+        <v>511.30</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="12.75">
       <c r="A53" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>21</v>
@@ -4281,39 +4215,39 @@
         <v>25</v>
       </c>
       <c r="K53" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L53" s="5">
         <v>5194</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N53" s="7">
         <v>46210</v>
       </c>
       <c r="O53" s="9">
-        <v>114.95</v>
+        <v>74.71</v>
       </c>
       <c r="P53" s="9">
-        <v>114.95</v>
+        <v>74.71</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="12.75">
       <c r="A54" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>21</v>
@@ -4334,13 +4268,13 @@
         <v>25</v>
       </c>
       <c r="K54" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L54" s="5">
         <v>5194</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N54" s="7">
         <v>46210</v>
@@ -4352,21 +4286,21 @@
         <v>114.95</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="12.75">
       <c r="A55" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>21</v>
@@ -4387,13 +4321,13 @@
         <v>25</v>
       </c>
       <c r="K55" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L55" s="5">
         <v>5194</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N55" s="7">
         <v>46210</v>
@@ -4405,21 +4339,21 @@
         <v>114.95</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="12.75">
       <c r="A56" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>21</v>
@@ -4440,39 +4374,39 @@
         <v>25</v>
       </c>
       <c r="K56" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L56" s="5">
         <v>5194</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N56" s="7">
         <v>46210</v>
       </c>
       <c r="O56" s="9">
-        <v>342.95</v>
+        <v>114.95</v>
       </c>
       <c r="P56" s="9">
-        <v>342.95</v>
+        <v>114.95</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="12.75">
       <c r="A57" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>21</v>
@@ -4493,39 +4427,39 @@
         <v>25</v>
       </c>
       <c r="K57" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L57" s="5">
         <v>5194</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N57" s="7">
         <v>46210</v>
       </c>
       <c r="O57" s="9">
-        <v>24.95</v>
+        <v>342.95</v>
       </c>
       <c r="P57" s="9">
-        <v>24.95</v>
+        <v>342.95</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="12.75">
       <c r="A58" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>21</v>
@@ -4546,39 +4480,39 @@
         <v>25</v>
       </c>
       <c r="K58" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L58" s="5">
         <v>5194</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N58" s="7">
         <v>46210</v>
       </c>
       <c r="O58" s="9">
-        <v>99.95</v>
+        <v>24.95</v>
       </c>
       <c r="P58" s="9">
-        <v>99.95</v>
+        <v>24.95</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="12.75">
       <c r="A59" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>21</v>
@@ -4599,39 +4533,39 @@
         <v>25</v>
       </c>
       <c r="K59" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L59" s="5">
         <v>5194</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N59" s="7">
         <v>46210</v>
       </c>
       <c r="O59" s="9">
-        <v>74.95</v>
+        <v>99.95</v>
       </c>
       <c r="P59" s="9">
-        <v>74.95</v>
+        <v>99.95</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="12.75">
       <c r="A60" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>21</v>
@@ -4652,39 +4586,39 @@
         <v>25</v>
       </c>
       <c r="K60" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L60" s="5">
         <v>5194</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N60" s="7">
         <v>46210</v>
       </c>
       <c r="O60" s="9">
-        <v>29.95</v>
+        <v>74.95</v>
       </c>
       <c r="P60" s="9">
-        <v>29.95</v>
+        <v>74.95</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="12.75">
       <c r="A61" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>21</v>
@@ -4705,39 +4639,39 @@
         <v>25</v>
       </c>
       <c r="K61" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L61" s="5">
         <v>5194</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N61" s="7">
         <v>46210</v>
       </c>
       <c r="O61" s="9">
-        <v>24.95</v>
+        <v>29.95</v>
       </c>
       <c r="P61" s="9">
-        <v>24.95</v>
+        <v>29.95</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="12.75">
       <c r="A62" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>21</v>
@@ -4758,39 +4692,39 @@
         <v>25</v>
       </c>
       <c r="K62" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L62" s="5">
         <v>5194</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N62" s="7">
         <v>46210</v>
       </c>
       <c r="O62" s="9">
-        <v>134.95</v>
+        <v>24.95</v>
       </c>
       <c r="P62" s="9">
-        <v>134.95</v>
+        <v>24.95</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="12.75">
       <c r="A63" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>21</v>
@@ -4811,39 +4745,39 @@
         <v>25</v>
       </c>
       <c r="K63" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L63" s="5">
         <v>5194</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N63" s="7">
         <v>46210</v>
       </c>
       <c r="O63" s="9">
-        <v>28.60</v>
+        <v>134.95</v>
       </c>
       <c r="P63" s="9">
-        <v>28.60</v>
+        <v>134.95</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="12.75">
       <c r="A64" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>21</v>
@@ -4864,39 +4798,39 @@
         <v>25</v>
       </c>
       <c r="K64" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L64" s="5">
         <v>5194</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N64" s="7">
         <v>46210</v>
       </c>
       <c r="O64" s="9">
-        <v>90</v>
+        <v>28.60</v>
       </c>
       <c r="P64" s="9">
-        <v>90</v>
+        <v>28.60</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="12.75">
       <c r="A65" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>21</v>
@@ -4908,7 +4842,7 @@
         <v>23</v>
       </c>
       <c r="H65" s="5">
-        <v>2620490</v>
+        <v>2620482</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>24</v>
@@ -4917,39 +4851,39 @@
         <v>25</v>
       </c>
       <c r="K65" s="5">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L65" s="5">
-        <v>1158</v>
+        <v>5194</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N65" s="7">
-        <v>46223</v>
+        <v>46210</v>
       </c>
       <c r="O65" s="9">
-        <v>1143.80</v>
+        <v>90</v>
       </c>
       <c r="P65" s="9">
-        <v>1143.80</v>
+        <v>90</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="12.75">
       <c r="A66" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>21</v>
@@ -4970,13 +4904,13 @@
         <v>25</v>
       </c>
       <c r="K66" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L66" s="5">
         <v>1158</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N66" s="7">
         <v>46223</v>
@@ -4988,21 +4922,21 @@
         <v>1143.80</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="12.75">
       <c r="A67" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>21</v>
@@ -5023,13 +4957,13 @@
         <v>25</v>
       </c>
       <c r="K67" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="5">
         <v>1158</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N67" s="7">
         <v>46223</v>
@@ -5041,21 +4975,21 @@
         <v>1143.80</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="12.75">
       <c r="A68" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>21</v>
@@ -5076,13 +5010,13 @@
         <v>25</v>
       </c>
       <c r="K68" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L68" s="5">
         <v>1158</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N68" s="7">
         <v>46223</v>
@@ -5094,21 +5028,21 @@
         <v>1143.80</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="12.75">
       <c r="A69" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>21</v>
@@ -5129,13 +5063,13 @@
         <v>25</v>
       </c>
       <c r="K69" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L69" s="5">
         <v>1158</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N69" s="7">
         <v>46223</v>
@@ -5147,21 +5081,21 @@
         <v>1143.80</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="12.75">
       <c r="A70" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>21</v>
@@ -5182,13 +5116,13 @@
         <v>25</v>
       </c>
       <c r="K70" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L70" s="5">
         <v>1158</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N70" s="7">
         <v>46223</v>
@@ -5200,21 +5134,21 @@
         <v>1143.80</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="12.75">
       <c r="A71" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>21</v>
@@ -5235,39 +5169,39 @@
         <v>25</v>
       </c>
       <c r="K71" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71" s="5">
         <v>1158</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N71" s="7">
         <v>46223</v>
       </c>
       <c r="O71" s="9">
-        <v>385.20</v>
+        <v>1143.80</v>
       </c>
       <c r="P71" s="9">
-        <v>385.20</v>
+        <v>1143.80</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="12.75">
       <c r="A72" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>21</v>
@@ -5288,39 +5222,39 @@
         <v>25</v>
       </c>
       <c r="K72" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L72" s="5">
         <v>1158</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N72" s="7">
         <v>46223</v>
       </c>
       <c r="O72" s="9">
-        <v>345.35</v>
+        <v>385.20</v>
       </c>
       <c r="P72" s="9">
-        <v>345.35</v>
+        <v>385.20</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="12.75">
       <c r="A73" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>21</v>
@@ -5341,39 +5275,39 @@
         <v>25</v>
       </c>
       <c r="K73" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L73" s="5">
         <v>1158</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="N73" s="7">
         <v>46223</v>
       </c>
       <c r="O73" s="9">
-        <v>125</v>
+        <v>345.35</v>
       </c>
       <c r="P73" s="9">
-        <v>125</v>
+        <v>345.35</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="12.75">
       <c r="A74" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>21</v>
@@ -5385,7 +5319,7 @@
         <v>23</v>
       </c>
       <c r="H74" s="5">
-        <v>2620498</v>
+        <v>2620490</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>24</v>
@@ -5394,39 +5328,39 @@
         <v>25</v>
       </c>
       <c r="K74" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L74" s="5">
-        <v>5057</v>
+        <v>1158</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="N74" s="7">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="O74" s="9">
-        <v>142.50</v>
+        <v>125</v>
       </c>
       <c r="P74" s="9">
-        <v>142.50</v>
+        <v>125</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="12.75">
       <c r="A75" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>21</v>
@@ -5447,39 +5381,39 @@
         <v>25</v>
       </c>
       <c r="K75" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L75" s="5">
         <v>5057</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N75" s="7">
         <v>46224</v>
       </c>
       <c r="O75" s="9">
-        <v>1567.50</v>
+        <v>6534.66</v>
       </c>
       <c r="P75" s="9">
-        <v>1567.50</v>
+        <v>33.62</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="12.75">
       <c r="A76" s="3" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>21</v>
@@ -5491,7 +5425,7 @@
         <v>23</v>
       </c>
       <c r="H76" s="5">
-        <v>2620498</v>
+        <v>2620072</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>24</v>
@@ -5500,39 +5434,39 @@
         <v>25</v>
       </c>
       <c r="K76" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L76" s="5">
-        <v>5057</v>
+        <v>1020</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="N76" s="7">
-        <v>46224</v>
+        <v>45937</v>
       </c>
       <c r="O76" s="9">
-        <v>3847.50</v>
+        <v>68708.51</v>
       </c>
       <c r="P76" s="9">
-        <v>3847.50</v>
+        <v>21678.57</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="12.75">
       <c r="A77" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>21</v>
@@ -5544,48 +5478,48 @@
         <v>23</v>
       </c>
       <c r="H77" s="5">
-        <v>2620498</v>
+        <v>2620149</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="K77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5">
-        <v>5057</v>
+        <v>1252</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N77" s="7">
-        <v>46224</v>
+        <v>45947</v>
       </c>
       <c r="O77" s="9">
-        <v>855</v>
+        <v>54000</v>
       </c>
       <c r="P77" s="9">
-        <v>855</v>
+        <v>18619.28</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="12.75">
       <c r="A78" s="3" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>21</v>
@@ -5597,48 +5531,48 @@
         <v>23</v>
       </c>
       <c r="H78" s="5">
-        <v>2620498</v>
+        <v>2620151</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="K78" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L78" s="5">
-        <v>5057</v>
+        <v>4034</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="N78" s="7">
-        <v>46224</v>
+        <v>45947</v>
       </c>
       <c r="O78" s="9">
-        <v>122.16</v>
+        <v>40000</v>
       </c>
       <c r="P78" s="9">
-        <v>122.16</v>
+        <v>3333.37</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="12.75">
       <c r="A79" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>21</v>
@@ -5650,154 +5584,154 @@
         <v>23</v>
       </c>
       <c r="H79" s="5">
-        <v>2620457</v>
+        <v>2620135</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="K79" s="5">
         <v>1</v>
       </c>
       <c r="L79" s="5">
-        <v>5187</v>
+        <v>1238</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="N79" s="7">
-        <v>46184</v>
+        <v>45947</v>
       </c>
       <c r="O79" s="9">
-        <v>2827</v>
+        <v>54000</v>
       </c>
       <c r="P79" s="9">
-        <v>2827</v>
+        <v>23520</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="12.75">
       <c r="A80" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="H80" s="5">
-        <v>2620457</v>
+        <v>2620342</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="K80" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="5">
-        <v>5187</v>
+        <v>1987</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="N80" s="7">
-        <v>46184</v>
+        <v>46069</v>
       </c>
       <c r="O80" s="9">
-        <v>56.25</v>
+        <v>3161.92</v>
       </c>
       <c r="P80" s="9">
-        <v>56.25</v>
+        <v>3161.92</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="12.75">
       <c r="A81" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="H81" s="5">
-        <v>2620072</v>
+        <v>2620389</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="K81" s="5">
         <v>1</v>
       </c>
       <c r="L81" s="5">
-        <v>1020</v>
+        <v>1402</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="N81" s="7">
-        <v>45937</v>
+        <v>46111</v>
       </c>
       <c r="O81" s="9">
-        <v>68708.51</v>
+        <v>555.80</v>
       </c>
       <c r="P81" s="9">
-        <v>21678.57</v>
+        <v>555.80</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="12.75">
       <c r="A82" s="3" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>21</v>
@@ -5809,48 +5743,48 @@
         <v>23</v>
       </c>
       <c r="H82" s="5">
-        <v>2620149</v>
+        <v>2620370</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="K82" s="5">
         <v>1</v>
       </c>
       <c r="L82" s="5">
-        <v>1252</v>
+        <v>2214</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="N82" s="7">
-        <v>45947</v>
+        <v>46097</v>
       </c>
       <c r="O82" s="9">
-        <v>54000</v>
+        <v>10560</v>
       </c>
       <c r="P82" s="9">
-        <v>22772.48</v>
+        <v>2795.04</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="12.75">
       <c r="A83" s="3" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>21</v>
@@ -5862,48 +5796,48 @@
         <v>23</v>
       </c>
       <c r="H83" s="5">
-        <v>2620151</v>
+        <v>2620162</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="K83" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" s="5">
-        <v>4034</v>
+        <v>1868</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="N83" s="7">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="O83" s="9">
-        <v>40000</v>
+        <v>33935.65</v>
       </c>
       <c r="P83" s="9">
-        <v>6666.70</v>
+        <v>19071.76</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="12.75">
       <c r="A84" s="3" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>21</v>
@@ -5915,154 +5849,154 @@
         <v>23</v>
       </c>
       <c r="H84" s="5">
-        <v>2620135</v>
+        <v>2620162</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="K84" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="5">
-        <v>1238</v>
+        <v>1868</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="N84" s="7">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="O84" s="9">
-        <v>54000</v>
+        <v>18453.49</v>
       </c>
       <c r="P84" s="9">
-        <v>23520</v>
+        <v>18453.49</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="12.75">
       <c r="A85" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="H85" s="5">
-        <v>2620342</v>
+        <v>2620162</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L85" s="5">
-        <v>1987</v>
+        <v>1868</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N85" s="7">
-        <v>46069</v>
+        <v>45953</v>
       </c>
       <c r="O85" s="9">
-        <v>3161.92</v>
+        <v>10116.86</v>
       </c>
       <c r="P85" s="9">
-        <v>3161.92</v>
+        <v>8397.66</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="12.75">
       <c r="A86" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="H86" s="5">
-        <v>2620389</v>
+        <v>2620040</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K86" s="5">
         <v>1</v>
       </c>
       <c r="L86" s="5">
-        <v>1402</v>
+        <v>3836</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N86" s="7">
-        <v>46111</v>
+        <v>45931</v>
       </c>
       <c r="O86" s="9">
-        <v>555.80</v>
+        <v>83500</v>
       </c>
       <c r="P86" s="9">
-        <v>555.80</v>
+        <v>0.04</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="12.75">
       <c r="A87" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>21</v>
@@ -6074,48 +6008,48 @@
         <v>23</v>
       </c>
       <c r="H87" s="5">
-        <v>2620370</v>
+        <v>2620407</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K87" s="5">
         <v>1</v>
       </c>
       <c r="L87" s="5">
-        <v>2214</v>
+        <v>1632</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="N87" s="7">
-        <v>46097</v>
+        <v>46129</v>
       </c>
       <c r="O87" s="9">
-        <v>10560</v>
+        <v>1620</v>
       </c>
       <c r="P87" s="9">
-        <v>2795.04</v>
+        <v>1620</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:17" ht="12.75">
       <c r="A88" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>21</v>
@@ -6127,48 +6061,48 @@
         <v>23</v>
       </c>
       <c r="H88" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K88" s="5">
         <v>2</v>
       </c>
       <c r="L88" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N88" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O88" s="9">
-        <v>33935.65</v>
+        <v>400</v>
       </c>
       <c r="P88" s="9">
-        <v>19071.76</v>
+        <v>400</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="12.75">
       <c r="A89" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
@@ -6180,48 +6114,48 @@
         <v>23</v>
       </c>
       <c r="H89" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K89" s="5">
         <v>3</v>
       </c>
       <c r="L89" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N89" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O89" s="9">
-        <v>18453.49</v>
+        <v>2042.50</v>
       </c>
       <c r="P89" s="9">
-        <v>18453.49</v>
+        <v>2042.50</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:17" ht="12.75">
       <c r="A90" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>21</v>
@@ -6233,48 +6167,48 @@
         <v>23</v>
       </c>
       <c r="H90" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K90" s="5">
         <v>4</v>
       </c>
       <c r="L90" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N90" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O90" s="9">
-        <v>10116.86</v>
+        <v>150</v>
       </c>
       <c r="P90" s="9">
-        <v>8397.66</v>
+        <v>150</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:17" ht="12.75">
       <c r="A91" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>21</v>
@@ -6286,48 +6220,48 @@
         <v>23</v>
       </c>
       <c r="H91" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K91" s="5">
         <v>5</v>
       </c>
       <c r="L91" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N91" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O91" s="9">
-        <v>8568.70</v>
+        <v>600</v>
       </c>
       <c r="P91" s="9">
-        <v>5430</v>
+        <v>600</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:17" ht="12.75">
       <c r="A92" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>21</v>
@@ -6339,48 +6273,48 @@
         <v>23</v>
       </c>
       <c r="H92" s="5">
-        <v>2620040</v>
+        <v>2620407</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K92" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L92" s="5">
-        <v>3836</v>
+        <v>1632</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N92" s="7">
-        <v>45931</v>
+        <v>46129</v>
       </c>
       <c r="O92" s="9">
-        <v>83500</v>
+        <v>600</v>
       </c>
       <c r="P92" s="9">
-        <v>6958.37</v>
+        <v>600</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="12.75">
       <c r="A93" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>21</v>
@@ -6392,48 +6326,48 @@
         <v>23</v>
       </c>
       <c r="H93" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K93" s="5">
         <v>1</v>
       </c>
       <c r="L93" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N93" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O93" s="9">
-        <v>1620</v>
+        <v>295</v>
       </c>
       <c r="P93" s="9">
-        <v>1620</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="12.75">
       <c r="A94" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>21</v>
@@ -6445,48 +6379,48 @@
         <v>23</v>
       </c>
       <c r="H94" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K94" s="5">
         <v>2</v>
       </c>
       <c r="L94" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N94" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O94" s="9">
-        <v>400</v>
+        <v>295</v>
       </c>
       <c r="P94" s="9">
-        <v>400</v>
+        <v>295</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:17" ht="12.75">
       <c r="A95" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>21</v>
@@ -6498,48 +6432,48 @@
         <v>23</v>
       </c>
       <c r="H95" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K95" s="5">
         <v>3</v>
       </c>
       <c r="L95" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N95" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O95" s="9">
-        <v>2042.50</v>
+        <v>295</v>
       </c>
       <c r="P95" s="9">
-        <v>2042.50</v>
+        <v>295</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:17" ht="12.75">
       <c r="A96" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>21</v>
@@ -6551,48 +6485,48 @@
         <v>23</v>
       </c>
       <c r="H96" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K96" s="5">
         <v>4</v>
       </c>
       <c r="L96" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N96" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O96" s="9">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="P96" s="9">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="12.75">
       <c r="A97" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>21</v>
@@ -6604,48 +6538,48 @@
         <v>23</v>
       </c>
       <c r="H97" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K97" s="5">
         <v>5</v>
       </c>
       <c r="L97" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N97" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O97" s="9">
-        <v>600</v>
+        <v>395</v>
       </c>
       <c r="P97" s="9">
-        <v>600</v>
+        <v>395</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:17" ht="12.75">
       <c r="A98" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>21</v>
@@ -6657,48 +6591,48 @@
         <v>23</v>
       </c>
       <c r="H98" s="5">
-        <v>2620407</v>
+        <v>2620487</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K98" s="5">
         <v>6</v>
       </c>
       <c r="L98" s="5">
-        <v>1632</v>
+        <v>5212</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N98" s="7">
-        <v>46129</v>
+        <v>46219</v>
       </c>
       <c r="O98" s="9">
-        <v>600</v>
+        <v>395</v>
       </c>
       <c r="P98" s="9">
-        <v>600</v>
+        <v>395</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="12.75">
       <c r="A99" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>21</v>
@@ -6716,42 +6650,42 @@
         <v>24</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K99" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L99" s="5">
         <v>5212</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N99" s="7">
         <v>46219</v>
       </c>
       <c r="O99" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="P99" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="12.75">
       <c r="A100" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>21</v>
@@ -6769,42 +6703,42 @@
         <v>24</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K100" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L100" s="5">
         <v>5212</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N100" s="7">
         <v>46219</v>
       </c>
       <c r="O100" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="P100" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="12.75">
       <c r="A101" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>21</v>
@@ -6822,42 +6756,42 @@
         <v>24</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K101" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L101" s="5">
         <v>5212</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N101" s="7">
         <v>46219</v>
       </c>
       <c r="O101" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="P101" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="12.75">
       <c r="A102" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>21</v>
@@ -6875,42 +6809,42 @@
         <v>24</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K102" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L102" s="5">
         <v>5212</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N102" s="7">
         <v>46219</v>
       </c>
       <c r="O102" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="P102" s="9">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="12.75">
       <c r="A103" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>21</v>
@@ -6928,42 +6862,42 @@
         <v>24</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K103" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L103" s="5">
         <v>5212</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N103" s="7">
         <v>46219</v>
       </c>
       <c r="O103" s="9">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="P103" s="9">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="12.75">
       <c r="A104" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>21</v>
@@ -6981,95 +6915,95 @@
         <v>24</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K104" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L104" s="5">
         <v>5212</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N104" s="7">
         <v>46219</v>
       </c>
       <c r="O104" s="9">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="P104" s="9">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="Q104" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:17" ht="12.75">
       <c r="A105" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="H105" s="5">
-        <v>2620487</v>
+        <v>2620263</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K105" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L105" s="5">
-        <v>5212</v>
+        <v>1136</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N105" s="7">
-        <v>46219</v>
+        <v>46002</v>
       </c>
       <c r="O105" s="9">
-        <v>395</v>
+        <v>134953.54</v>
       </c>
       <c r="P105" s="9">
-        <v>395</v>
+        <v>35211.86</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:17" ht="12.75">
       <c r="A106" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>21</v>
@@ -7081,48 +7015,48 @@
         <v>23</v>
       </c>
       <c r="H106" s="5">
-        <v>2620487</v>
+        <v>2620167</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="K106" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L106" s="5">
-        <v>5212</v>
+        <v>1620</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N106" s="7">
-        <v>46219</v>
+        <v>45954</v>
       </c>
       <c r="O106" s="9">
-        <v>395</v>
+        <v>23400</v>
       </c>
       <c r="P106" s="9">
-        <v>395</v>
+        <v>8025</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="12.75">
       <c r="A107" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>21</v>
@@ -7134,48 +7068,48 @@
         <v>23</v>
       </c>
       <c r="H107" s="5">
-        <v>2620487</v>
+        <v>2620167</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="K107" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L107" s="5">
-        <v>5212</v>
+        <v>1620</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N107" s="7">
-        <v>46219</v>
+        <v>45954</v>
       </c>
       <c r="O107" s="9">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="P107" s="9">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="Q107" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:17" ht="12.75">
       <c r="A108" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>21</v>
@@ -7187,48 +7121,48 @@
         <v>23</v>
       </c>
       <c r="H108" s="5">
-        <v>2620487</v>
+        <v>2620167</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="K108" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L108" s="5">
-        <v>5212</v>
+        <v>1620</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N108" s="7">
-        <v>46219</v>
+        <v>45954</v>
       </c>
       <c r="O108" s="9">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="P108" s="9">
-        <v>395</v>
+        <v>225</v>
       </c>
       <c r="Q108" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="12.75">
       <c r="A109" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>21</v>
@@ -7240,48 +7174,48 @@
         <v>23</v>
       </c>
       <c r="H109" s="5">
-        <v>2620487</v>
+        <v>2620167</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="K109" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L109" s="5">
-        <v>5212</v>
+        <v>1620</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N109" s="7">
-        <v>46219</v>
+        <v>45954</v>
       </c>
       <c r="O109" s="9">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="P109" s="9">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="Q109" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="12.75">
       <c r="A110" s="3" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>21</v>
@@ -7293,101 +7227,101 @@
         <v>23</v>
       </c>
       <c r="H110" s="5">
-        <v>2620487</v>
+        <v>2620392</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="K110" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L110" s="5">
-        <v>5212</v>
+        <v>1620</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N110" s="7">
-        <v>46219</v>
+        <v>46111</v>
       </c>
       <c r="O110" s="9">
-        <v>358</v>
+        <v>8690</v>
       </c>
       <c r="P110" s="9">
-        <v>358</v>
+        <v>8690</v>
       </c>
       <c r="Q110" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111" spans="1:17" ht="12.75">
       <c r="A111" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="5">
+        <v>2620392</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J111" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="K111" s="5">
+        <v>2</v>
+      </c>
+      <c r="L111" s="5">
+        <v>1620</v>
+      </c>
+      <c r="M111" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H111" s="5">
-        <v>2620263</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K111" s="5">
-        <v>1</v>
-      </c>
-      <c r="L111" s="5">
-        <v>1136</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="N111" s="7">
-        <v>46002</v>
+        <v>46111</v>
       </c>
       <c r="O111" s="9">
-        <v>134953.54</v>
+        <v>400</v>
       </c>
       <c r="P111" s="9">
-        <v>35211.86</v>
+        <v>400</v>
       </c>
       <c r="Q111" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="12.75">
       <c r="A112" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>21</v>
@@ -7399,48 +7333,48 @@
         <v>23</v>
       </c>
       <c r="H112" s="5">
-        <v>2620167</v>
+        <v>2620382</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K112" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="5">
-        <v>1620</v>
+        <v>2968</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N112" s="7">
-        <v>45954</v>
+        <v>46101</v>
       </c>
       <c r="O112" s="9">
-        <v>23400</v>
+        <v>10000</v>
       </c>
       <c r="P112" s="9">
-        <v>8025</v>
+        <v>2958.46</v>
       </c>
       <c r="Q112" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="12.75">
       <c r="A113" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>21</v>
@@ -7452,48 +7386,48 @@
         <v>23</v>
       </c>
       <c r="H113" s="5">
-        <v>2620167</v>
+        <v>2620388</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="5">
-        <v>1620</v>
+        <v>5125</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N113" s="7">
-        <v>45954</v>
+        <v>46107</v>
       </c>
       <c r="O113" s="9">
-        <v>250</v>
+        <v>5250</v>
       </c>
       <c r="P113" s="9">
-        <v>250</v>
+        <v>1312.50</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:17" ht="12.75">
       <c r="A114" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>21</v>
@@ -7505,48 +7439,48 @@
         <v>23</v>
       </c>
       <c r="H114" s="5">
-        <v>2620167</v>
+        <v>2620444</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K114" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L114" s="5">
-        <v>1620</v>
+        <v>4905</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="N114" s="7">
-        <v>45954</v>
+        <v>46169</v>
       </c>
       <c r="O114" s="9">
-        <v>375</v>
+        <v>795</v>
       </c>
       <c r="P114" s="9">
-        <v>225</v>
+        <v>795</v>
       </c>
       <c r="Q114" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115" spans="1:17" ht="12.75">
       <c r="A115" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>21</v>
@@ -7558,48 +7492,48 @@
         <v>23</v>
       </c>
       <c r="H115" s="5">
-        <v>2620167</v>
+        <v>2620444</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K115" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L115" s="5">
-        <v>1620</v>
+        <v>4905</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="N115" s="7">
-        <v>45954</v>
+        <v>46169</v>
       </c>
       <c r="O115" s="9">
-        <v>500</v>
+        <v>795</v>
       </c>
       <c r="P115" s="9">
-        <v>500</v>
+        <v>795</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:17" ht="12.75">
       <c r="A116" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>21</v>
@@ -7611,101 +7545,101 @@
         <v>23</v>
       </c>
       <c r="H116" s="5">
-        <v>2620392</v>
+        <v>2620444</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K116" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L116" s="5">
-        <v>1620</v>
+        <v>4905</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="N116" s="7">
-        <v>46111</v>
+        <v>46169</v>
       </c>
       <c r="O116" s="9">
-        <v>8690</v>
+        <v>795</v>
       </c>
       <c r="P116" s="9">
-        <v>8690</v>
+        <v>795</v>
       </c>
       <c r="Q116" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="117" spans="1:17" ht="12.75">
       <c r="A117" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="H117" s="5">
-        <v>2620392</v>
+        <v>2620382</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K117" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L117" s="5">
-        <v>1620</v>
+        <v>2968</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N117" s="7">
-        <v>46111</v>
+        <v>46101</v>
       </c>
       <c r="O117" s="9">
-        <v>400</v>
+        <v>18000</v>
       </c>
       <c r="P117" s="9">
-        <v>400</v>
+        <v>8308.08</v>
       </c>
       <c r="Q117" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="118" spans="1:17" ht="12.75">
       <c r="A118" s="3" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>68</v>
+        <v>212</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>21</v>
@@ -7717,48 +7651,48 @@
         <v>23</v>
       </c>
       <c r="H118" s="5">
-        <v>2620382</v>
+        <v>2620089</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K118" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L118" s="5">
-        <v>2968</v>
+        <v>1206</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N118" s="7">
-        <v>46101</v>
+        <v>45943</v>
       </c>
       <c r="O118" s="9">
-        <v>10000</v>
+        <v>2755.20</v>
       </c>
       <c r="P118" s="9">
-        <v>3952.96</v>
+        <v>495.58</v>
       </c>
       <c r="Q118" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:17" ht="12.75">
       <c r="A119" s="3" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>68</v>
+        <v>212</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>21</v>
@@ -7770,48 +7704,48 @@
         <v>23</v>
       </c>
       <c r="H119" s="5">
-        <v>2620388</v>
+        <v>2620089</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="5">
-        <v>5125</v>
+        <v>1206</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="N119" s="7">
-        <v>46107</v>
+        <v>45943</v>
       </c>
       <c r="O119" s="9">
-        <v>5250</v>
+        <v>9360</v>
       </c>
       <c r="P119" s="9">
-        <v>1312.50</v>
+        <v>2966.03</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="1:17" ht="12.75">
       <c r="A120" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="C120" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>21</v>
@@ -7823,48 +7757,48 @@
         <v>23</v>
       </c>
       <c r="H120" s="5">
-        <v>2620444</v>
+        <v>2620094</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K120" s="5">
         <v>1</v>
       </c>
       <c r="L120" s="5">
-        <v>4905</v>
+        <v>1049</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="N120" s="7">
-        <v>46169</v>
+        <v>45943</v>
       </c>
       <c r="O120" s="9">
-        <v>795</v>
+        <v>25000</v>
       </c>
       <c r="P120" s="9">
-        <v>795</v>
+        <v>15103.43</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="1:17" ht="12.75">
       <c r="A121" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="C121" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>21</v>
@@ -7876,48 +7810,48 @@
         <v>23</v>
       </c>
       <c r="H121" s="5">
-        <v>2620444</v>
+        <v>2620095</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K121" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="5">
-        <v>4905</v>
+        <v>1974</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="N121" s="7">
-        <v>46169</v>
+        <v>45943</v>
       </c>
       <c r="O121" s="9">
-        <v>795</v>
+        <v>35000</v>
       </c>
       <c r="P121" s="9">
-        <v>795</v>
+        <v>3236.29</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:17" ht="12.75">
       <c r="A122" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="C122" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>21</v>
@@ -7929,101 +7863,101 @@
         <v>23</v>
       </c>
       <c r="H122" s="5">
-        <v>2620444</v>
+        <v>2620148</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K122" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122" s="5">
-        <v>4905</v>
+        <v>1689</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="N122" s="7">
-        <v>46169</v>
+        <v>45947</v>
       </c>
       <c r="O122" s="9">
-        <v>795</v>
+        <v>36574</v>
       </c>
       <c r="P122" s="9">
-        <v>795</v>
+        <v>38.43</v>
       </c>
       <c r="Q122" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:17" ht="12.75">
       <c r="A123" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H123" s="5">
+        <v>2620158</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J123" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H123" s="5">
-        <v>2620382</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="K123" s="5">
         <v>1</v>
       </c>
       <c r="L123" s="5">
-        <v>2968</v>
+        <v>1464</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="N123" s="7">
-        <v>46101</v>
+        <v>45952</v>
       </c>
       <c r="O123" s="9">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="P123" s="9">
-        <v>10481.58</v>
+        <v>2822.66</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="12.75">
       <c r="A124" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>21</v>
@@ -8035,31 +7969,31 @@
         <v>23</v>
       </c>
       <c r="H124" s="5">
-        <v>2620089</v>
+        <v>2620159</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K124" s="5">
         <v>1</v>
       </c>
       <c r="L124" s="5">
-        <v>1206</v>
+        <v>1464</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N124" s="7">
-        <v>45943</v>
+        <v>45952</v>
       </c>
       <c r="O124" s="9">
-        <v>2755.20</v>
+        <v>75000</v>
       </c>
       <c r="P124" s="9">
-        <v>495.58</v>
+        <v>14676.08</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>224</v>
@@ -8067,16 +8001,16 @@
     </row>
     <row r="125" spans="1:17" ht="12.75">
       <c r="A125" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>21</v>
@@ -8088,48 +8022,48 @@
         <v>23</v>
       </c>
       <c r="H125" s="5">
-        <v>2620089</v>
+        <v>2620517</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K125" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L125" s="5">
-        <v>1206</v>
+        <v>5163</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N125" s="7">
-        <v>45943</v>
+        <v>46247</v>
       </c>
       <c r="O125" s="9">
-        <v>9360</v>
+        <v>1450</v>
       </c>
       <c r="P125" s="9">
-        <v>2966.03</v>
+        <v>1450</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="12.75">
       <c r="A126" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>21</v>
@@ -8141,48 +8075,48 @@
         <v>23</v>
       </c>
       <c r="H126" s="5">
-        <v>2620094</v>
+        <v>2620517</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K126" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="5">
-        <v>1049</v>
+        <v>5163</v>
       </c>
       <c r="M126" s="3" t="s">
         <v>225</v>
       </c>
       <c r="N126" s="7">
-        <v>45943</v>
+        <v>46247</v>
       </c>
       <c r="O126" s="9">
-        <v>25000</v>
+        <v>2100</v>
       </c>
       <c r="P126" s="9">
-        <v>19011.14</v>
+        <v>2100</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="127" spans="1:17" ht="12.75">
       <c r="A127" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>21</v>
@@ -8194,48 +8128,48 @@
         <v>23</v>
       </c>
       <c r="H127" s="5">
-        <v>2620095</v>
+        <v>2620093</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K127" s="5">
         <v>1</v>
       </c>
       <c r="L127" s="5">
-        <v>1974</v>
+        <v>2106</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N127" s="7">
         <v>45943</v>
       </c>
       <c r="O127" s="9">
-        <v>35000</v>
+        <v>3364.55</v>
       </c>
       <c r="P127" s="9">
-        <v>4819.64</v>
+        <v>0.01</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="1:17" ht="12.75">
       <c r="A128" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>21</v>
@@ -8247,48 +8181,48 @@
         <v>23</v>
       </c>
       <c r="H128" s="5">
-        <v>2620148</v>
+        <v>2620147</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K128" s="5">
         <v>1</v>
       </c>
       <c r="L128" s="5">
-        <v>1689</v>
+        <v>2214</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="N128" s="7">
         <v>45947</v>
       </c>
       <c r="O128" s="9">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="P128" s="9">
-        <v>14.28</v>
+        <v>438.69</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="12.75">
       <c r="A129" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>21</v>
@@ -8300,48 +8234,48 @@
         <v>23</v>
       </c>
       <c r="H129" s="5">
-        <v>2620158</v>
+        <v>2620249</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K129" s="5">
         <v>1</v>
       </c>
       <c r="L129" s="5">
-        <v>1464</v>
+        <v>4921</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N129" s="7">
-        <v>45952</v>
+        <v>45999</v>
       </c>
       <c r="O129" s="9">
-        <v>8000</v>
+        <v>13400</v>
       </c>
       <c r="P129" s="9">
-        <v>3078.23</v>
+        <v>1845.67</v>
       </c>
       <c r="Q129" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" spans="1:17" ht="12.75">
       <c r="A130" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>21</v>
@@ -8353,48 +8287,48 @@
         <v>23</v>
       </c>
       <c r="H130" s="5">
-        <v>2620159</v>
+        <v>2620379</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K130" s="5">
         <v>1</v>
       </c>
       <c r="L130" s="5">
-        <v>1464</v>
+        <v>2214</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="N130" s="7">
-        <v>45952</v>
+        <v>46098</v>
       </c>
       <c r="O130" s="9">
-        <v>75000</v>
+        <v>600</v>
       </c>
       <c r="P130" s="9">
-        <v>21379.65</v>
+        <v>276.46</v>
       </c>
       <c r="Q130" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:17" ht="12.75">
       <c r="A131" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>21</v>
@@ -8406,48 +8340,48 @@
         <v>23</v>
       </c>
       <c r="H131" s="5">
-        <v>2620093</v>
+        <v>2620379</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K131" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L131" s="5">
-        <v>2106</v>
+        <v>2214</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="N131" s="7">
-        <v>45943</v>
+        <v>46098</v>
       </c>
       <c r="O131" s="9">
-        <v>3364.55</v>
+        <v>2476</v>
       </c>
       <c r="P131" s="9">
-        <v>0.01</v>
+        <v>2476</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="12.75">
       <c r="A132" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>21</v>
@@ -8459,31 +8393,31 @@
         <v>23</v>
       </c>
       <c r="H132" s="5">
-        <v>2620147</v>
+        <v>2620379</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K132" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L132" s="5">
         <v>2214</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N132" s="7">
-        <v>45947</v>
+        <v>46098</v>
       </c>
       <c r="O132" s="9">
-        <v>4000</v>
+        <v>788.13</v>
       </c>
       <c r="P132" s="9">
-        <v>438.69</v>
+        <v>314.12</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>235</v>
@@ -8491,16 +8425,16 @@
     </row>
     <row r="133" spans="1:17" ht="12.75">
       <c r="A133" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>21</v>
@@ -8512,48 +8446,48 @@
         <v>23</v>
       </c>
       <c r="H133" s="5">
-        <v>2620249</v>
+        <v>2620090</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K133" s="5">
         <v>1</v>
       </c>
       <c r="L133" s="5">
-        <v>4921</v>
+        <v>2018</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N133" s="7">
-        <v>45999</v>
+        <v>45943</v>
       </c>
       <c r="O133" s="9">
-        <v>13400</v>
+        <v>9100</v>
       </c>
       <c r="P133" s="9">
-        <v>1845.67</v>
+        <v>1487.50</v>
       </c>
       <c r="Q133" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:17" ht="12.75">
       <c r="A134" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>21</v>
@@ -8565,48 +8499,48 @@
         <v>23</v>
       </c>
       <c r="H134" s="5">
-        <v>2620379</v>
+        <v>2620146</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K134" s="5">
         <v>1</v>
       </c>
       <c r="L134" s="5">
-        <v>2214</v>
+        <v>4767</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="N134" s="7">
-        <v>46098</v>
+        <v>45947</v>
       </c>
       <c r="O134" s="9">
-        <v>600</v>
+        <v>3600</v>
       </c>
       <c r="P134" s="9">
-        <v>276.46</v>
+        <v>2550</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="12.75">
       <c r="A135" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>21</v>
@@ -8618,737 +8552,737 @@
         <v>23</v>
       </c>
       <c r="H135" s="5">
-        <v>2620379</v>
+        <v>2620255</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="K135" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L135" s="5">
-        <v>2214</v>
+        <v>2147</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="N135" s="7">
-        <v>46098</v>
+        <v>46000</v>
       </c>
       <c r="O135" s="9">
-        <v>2476</v>
+        <v>30000</v>
       </c>
       <c r="P135" s="9">
-        <v>2476</v>
+        <v>7500</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="136" spans="1:17" ht="12.75">
       <c r="A136" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H136" s="5">
-        <v>2620379</v>
+        <v>2620295</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="K136" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L136" s="5">
-        <v>2214</v>
+        <v>3985</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="N136" s="7">
-        <v>46098</v>
+        <v>46030</v>
       </c>
       <c r="O136" s="9">
-        <v>788.13</v>
+        <v>10000</v>
       </c>
       <c r="P136" s="9">
-        <v>314.12</v>
+        <v>2611.86</v>
       </c>
       <c r="Q136" s="3" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" spans="1:17" ht="12.75">
       <c r="A137" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H137" s="5">
-        <v>2620497</v>
+        <v>2620295</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="K137" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L137" s="5">
-        <v>5086</v>
+        <v>3985</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="N137" s="7">
-        <v>46224</v>
+        <v>46030</v>
       </c>
       <c r="O137" s="9">
-        <v>675</v>
+        <v>21000</v>
       </c>
       <c r="P137" s="9">
-        <v>675</v>
+        <v>8291.88</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
     <row r="138" spans="1:17" ht="12.75">
       <c r="A138" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H138" s="5">
-        <v>2620497</v>
+        <v>2620098</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="K138" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L138" s="5">
-        <v>5086</v>
+        <v>1227</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="N138" s="7">
-        <v>46224</v>
+        <v>45943</v>
       </c>
       <c r="O138" s="9">
-        <v>241.18</v>
+        <v>18082.30</v>
       </c>
       <c r="P138" s="9">
-        <v>241.18</v>
+        <v>4285.45</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" spans="1:17" ht="12.75">
       <c r="A139" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H139" s="5">
-        <v>2620497</v>
+        <v>2620327</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="K139" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L139" s="5">
-        <v>5086</v>
+        <v>1650</v>
       </c>
       <c r="M139" s="3" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="N139" s="7">
-        <v>46224</v>
+        <v>46057</v>
       </c>
       <c r="O139" s="9">
-        <v>100</v>
+        <v>12000</v>
       </c>
       <c r="P139" s="9">
-        <v>100</v>
+        <v>5700</v>
       </c>
       <c r="Q139" s="3" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="140" spans="1:17" ht="12.75">
       <c r="A140" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H140" s="5">
-        <v>2620090</v>
+        <v>2620327</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="K140" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L140" s="5">
-        <v>2018</v>
+        <v>1650</v>
       </c>
       <c r="M140" s="3" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N140" s="7">
-        <v>45943</v>
+        <v>46057</v>
       </c>
       <c r="O140" s="9">
-        <v>9100</v>
+        <v>6900</v>
       </c>
       <c r="P140" s="9">
-        <v>1487.50</v>
+        <v>600</v>
       </c>
       <c r="Q140" s="3" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:17" ht="12.75">
       <c r="A141" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H141" s="5">
-        <v>2620146</v>
+        <v>2620104</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="K141" s="5">
         <v>1</v>
       </c>
       <c r="L141" s="5">
-        <v>4767</v>
+        <v>3600</v>
       </c>
       <c r="M141" s="3" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="N141" s="7">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="O141" s="9">
-        <v>3600</v>
+        <v>20556.12</v>
       </c>
       <c r="P141" s="9">
-        <v>2550</v>
+        <v>5139.15</v>
       </c>
       <c r="Q141" s="3" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="142" spans="1:17" ht="12.75">
       <c r="A142" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C142" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F142" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="G142" s="3" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="H142" s="5">
-        <v>2620255</v>
+        <v>2620493</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K142" s="5">
         <v>1</v>
       </c>
       <c r="L142" s="5">
-        <v>2147</v>
+        <v>1398</v>
       </c>
       <c r="M142" s="3" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="N142" s="7">
-        <v>46000</v>
+        <v>46223</v>
       </c>
       <c r="O142" s="9">
-        <v>30000</v>
+        <v>5640</v>
       </c>
       <c r="P142" s="9">
-        <v>7500</v>
+        <v>1880</v>
       </c>
       <c r="Q142" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:17" ht="12.75">
       <c r="A143" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H143" s="5">
-        <v>2620295</v>
+        <v>2620051</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="K143" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L143" s="5">
-        <v>3985</v>
+        <v>4906</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="N143" s="7">
-        <v>46030</v>
+        <v>45933</v>
       </c>
       <c r="O143" s="9">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="P143" s="9">
-        <v>2611.86</v>
+        <v>3871.33</v>
       </c>
       <c r="Q143" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:17" ht="12.75">
       <c r="A144" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H144" s="5">
-        <v>2620295</v>
+        <v>2620152</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="K144" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L144" s="5">
-        <v>3985</v>
+        <v>1954</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="N144" s="7">
-        <v>46030</v>
+        <v>45950</v>
       </c>
       <c r="O144" s="9">
-        <v>21000</v>
+        <v>40000</v>
       </c>
       <c r="P144" s="9">
-        <v>8291.88</v>
+        <v>20087.50</v>
       </c>
       <c r="Q144" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="145" spans="1:17" ht="12.75">
       <c r="A145" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H145" s="5">
-        <v>2620327</v>
+        <v>2620284</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K145" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L145" s="5">
-        <v>1650</v>
+        <v>3099</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="N145" s="7">
-        <v>46057</v>
+        <v>46028</v>
       </c>
       <c r="O145" s="9">
-        <v>12000</v>
+        <v>13210.50</v>
       </c>
       <c r="P145" s="9">
-        <v>5700</v>
+        <v>777.75</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="146" spans="1:17" ht="12.75">
       <c r="A146" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H146" s="5">
-        <v>2620327</v>
+        <v>2620284</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K146" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L146" s="5">
-        <v>1650</v>
+        <v>3099</v>
       </c>
       <c r="M146" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="N146" s="7">
-        <v>46057</v>
+        <v>46028</v>
       </c>
       <c r="O146" s="9">
-        <v>6900</v>
+        <v>4000</v>
       </c>
       <c r="P146" s="9">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="Q146" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="147" spans="1:17" ht="12.75">
       <c r="A147" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H147" s="5">
-        <v>2620475</v>
+        <v>2620296</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K147" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" s="5">
-        <v>5204</v>
+        <v>3739</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="N147" s="7">
-        <v>46204</v>
+        <v>46034</v>
       </c>
       <c r="O147" s="9">
-        <v>4990</v>
+        <v>5336</v>
       </c>
       <c r="P147" s="9">
-        <v>2495</v>
+        <v>1509.50</v>
       </c>
       <c r="Q147" s="3" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:17" ht="12.75">
       <c r="A148" s="3" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>68</v>
+        <v>283</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>69</v>
+        <v>284</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>259</v>
+        <v>23</v>
       </c>
       <c r="H148" s="5">
-        <v>2620493</v>
+        <v>2620061</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K148" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148" s="5">
-        <v>1398</v>
+        <v>4918</v>
       </c>
       <c r="M148" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="N148" s="7">
-        <v>46223</v>
+        <v>45933</v>
       </c>
       <c r="O148" s="9">
-        <v>5640</v>
+        <v>5963</v>
       </c>
       <c r="P148" s="9">
-        <v>3760</v>
+        <v>355</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="149" spans="1:17" ht="12.75">
       <c r="A149" s="3" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>21</v>
@@ -9360,48 +9294,48 @@
         <v>23</v>
       </c>
       <c r="H149" s="5">
-        <v>2620051</v>
+        <v>2620050</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="K149" s="5">
         <v>1</v>
       </c>
       <c r="L149" s="5">
-        <v>4906</v>
+        <v>1417</v>
       </c>
       <c r="M149" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="N149" s="7">
         <v>45933</v>
       </c>
       <c r="O149" s="9">
-        <v>20000</v>
+        <v>1873</v>
       </c>
       <c r="P149" s="9">
-        <v>3871.33</v>
+        <v>165.42</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="150" spans="1:17" ht="12.75">
       <c r="A150" s="3" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>21</v>
@@ -9413,48 +9347,48 @@
         <v>23</v>
       </c>
       <c r="H150" s="5">
-        <v>2620152</v>
+        <v>2620153</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="K150" s="5">
         <v>1</v>
       </c>
       <c r="L150" s="5">
-        <v>1954</v>
+        <v>1755</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="N150" s="7">
         <v>45950</v>
       </c>
       <c r="O150" s="9">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="P150" s="9">
-        <v>20087.50</v>
+        <v>3623</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:17" ht="12.75">
       <c r="A151" s="3" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>21</v>
@@ -9466,564 +9400,34 @@
         <v>23</v>
       </c>
       <c r="H151" s="5">
-        <v>2620284</v>
+        <v>2620495</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="K151" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L151" s="5">
-        <v>3099</v>
+        <v>1071</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="N151" s="7">
-        <v>46028</v>
+        <v>46223</v>
       </c>
       <c r="O151" s="9">
-        <v>13210.50</v>
+        <v>3852</v>
       </c>
       <c r="P151" s="9">
-        <v>777.75</v>
+        <v>3852</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" ht="12.75">
-      <c r="A152" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H152" s="5">
-        <v>2620284</v>
-      </c>
-      <c r="I152" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K152" s="5">
-        <v>4</v>
-      </c>
-      <c r="L152" s="5">
-        <v>3099</v>
-      </c>
-      <c r="M152" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="N152" s="7">
-        <v>46028</v>
-      </c>
-      <c r="O152" s="9">
-        <v>4000</v>
-      </c>
-      <c r="P152" s="9">
-        <v>4000</v>
-      </c>
-      <c r="Q152" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" ht="12.75">
-      <c r="A153" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H153" s="5">
-        <v>2620420</v>
-      </c>
-      <c r="I153" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K153" s="5">
-        <v>1</v>
-      </c>
-      <c r="L153" s="5">
-        <v>1465</v>
-      </c>
-      <c r="M153" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="N153" s="7">
-        <v>46143</v>
-      </c>
-      <c r="O153" s="9">
-        <v>29117</v>
-      </c>
-      <c r="P153" s="9">
-        <v>29117</v>
-      </c>
-      <c r="Q153" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" ht="12.75">
-      <c r="A154" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H154" s="5">
-        <v>2620296</v>
-      </c>
-      <c r="I154" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J154" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K154" s="5">
-        <v>2</v>
-      </c>
-      <c r="L154" s="5">
-        <v>3739</v>
-      </c>
-      <c r="M154" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="N154" s="7">
-        <v>46034</v>
-      </c>
-      <c r="O154" s="9">
-        <v>5336</v>
-      </c>
-      <c r="P154" s="9">
-        <v>1509.50</v>
-      </c>
-      <c r="Q154" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" ht="12.75">
-      <c r="A155" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H155" s="5">
-        <v>2620061</v>
-      </c>
-      <c r="I155" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J155" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K155" s="5">
-        <v>2</v>
-      </c>
-      <c r="L155" s="5">
-        <v>4918</v>
-      </c>
-      <c r="M155" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="N155" s="7">
-        <v>45933</v>
-      </c>
-      <c r="O155" s="9">
-        <v>5963</v>
-      </c>
-      <c r="P155" s="9">
-        <v>355</v>
-      </c>
-      <c r="Q155" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" ht="12.75">
-      <c r="A156" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C156" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H156" s="5">
-        <v>2620050</v>
-      </c>
-      <c r="I156" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J156" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K156" s="5">
-        <v>1</v>
-      </c>
-      <c r="L156" s="5">
-        <v>1417</v>
-      </c>
-      <c r="M156" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="N156" s="7">
-        <v>45933</v>
-      </c>
-      <c r="O156" s="9">
-        <v>1873</v>
-      </c>
-      <c r="P156" s="9">
-        <v>362.47</v>
-      </c>
-      <c r="Q156" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" ht="12.75">
-      <c r="A157" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H157" s="5">
-        <v>2620153</v>
-      </c>
-      <c r="I157" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J157" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K157" s="5">
-        <v>1</v>
-      </c>
-      <c r="L157" s="5">
-        <v>1755</v>
-      </c>
-      <c r="M157" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="N157" s="7">
-        <v>45950</v>
-      </c>
-      <c r="O157" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P157" s="9">
-        <v>3623</v>
-      </c>
-      <c r="Q157" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" ht="12.75">
-      <c r="A158" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H158" s="5">
-        <v>2620492</v>
-      </c>
-      <c r="I158" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J158" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K158" s="5">
-        <v>1</v>
-      </c>
-      <c r="L158" s="5">
-        <v>1071</v>
-      </c>
-      <c r="M158" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="N158" s="7">
-        <v>46223</v>
-      </c>
-      <c r="O158" s="9">
-        <v>434</v>
-      </c>
-      <c r="P158" s="9">
-        <v>434</v>
-      </c>
-      <c r="Q158" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" ht="12.75">
-      <c r="A159" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H159" s="5">
-        <v>2620495</v>
-      </c>
-      <c r="I159" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J159" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K159" s="5">
-        <v>1</v>
-      </c>
-      <c r="L159" s="5">
-        <v>1071</v>
-      </c>
-      <c r="M159" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="N159" s="7">
-        <v>46223</v>
-      </c>
-      <c r="O159" s="9">
-        <v>3852</v>
-      </c>
-      <c r="P159" s="9">
-        <v>3852</v>
-      </c>
-      <c r="Q159" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" ht="12.75">
-      <c r="A160" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H160" s="5">
-        <v>2620176</v>
-      </c>
-      <c r="I160" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J160" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K160" s="5">
-        <v>4</v>
-      </c>
-      <c r="L160" s="5">
-        <v>1216</v>
-      </c>
-      <c r="M160" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="N160" s="7">
-        <v>45960</v>
-      </c>
-      <c r="O160" s="9">
-        <v>10700</v>
-      </c>
-      <c r="P160" s="9">
-        <v>2675</v>
-      </c>
-      <c r="Q160" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" ht="12.75">
-      <c r="A161" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H161" s="5">
-        <v>2620496</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J161" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K161" s="5">
-        <v>1</v>
-      </c>
-      <c r="L161" s="5">
-        <v>5090</v>
-      </c>
-      <c r="M161" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="N161" s="7">
-        <v>46223</v>
-      </c>
-      <c r="O161" s="9">
-        <v>3867</v>
-      </c>
-      <c r="P161" s="9">
-        <v>3867</v>
-      </c>
-      <c r="Q161" s="3" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/data/open-pos.xlsx
+++ b/data/open-pos.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="222">
   <si>
     <t>Account</t>
   </si>
@@ -143,204 +143,141 @@
     <t>Fuel-Station 213 &amp; 214 FY26</t>
   </si>
   <si>
-    <t>Fuel Station 211</t>
-  </si>
-  <si>
-    <t>100-30-340-5201-</t>
+    <t>100-30-340-5204-</t>
+  </si>
+  <si>
+    <t>Maint - Automobiles</t>
+  </si>
+  <si>
+    <t>5204</t>
+  </si>
+  <si>
+    <t>SIDDONS-MARTIN EMERGENCY GROU</t>
+  </si>
+  <si>
+    <t>FY26 VEHICLE MAINTENANCE  HGAC FS</t>
+  </si>
+  <si>
+    <t>100-30-340-5374-</t>
+  </si>
+  <si>
+    <t>Special Services</t>
+  </si>
+  <si>
+    <t>5374</t>
+  </si>
+  <si>
+    <t>CITY OF DESOTO</t>
+  </si>
+  <si>
+    <t>Full Time Annual Salary</t>
+  </si>
+  <si>
+    <t>Uniforms</t>
+  </si>
+  <si>
+    <t>Certification Pay</t>
+  </si>
+  <si>
+    <t>Medical Benefit (HSA Medical Plan</t>
+  </si>
+  <si>
+    <t>Dental Insurance Benefit</t>
+  </si>
+  <si>
+    <t>Basic Term Life Benefit</t>
+  </si>
+  <si>
+    <t>Group Long Term Benefit</t>
+  </si>
+  <si>
+    <t>FIRE-DEX GW, LLC</t>
+  </si>
+  <si>
+    <t>Bunker Gear Cleaning &amp; Inspection</t>
+  </si>
+  <si>
+    <t>100-30-340-5616-</t>
+  </si>
+  <si>
+    <t>5616</t>
+  </si>
+  <si>
+    <t>CASCO INDUSTRIES, INC</t>
+  </si>
+  <si>
+    <t>PPE- COATS, PANTS, HELMETS, BOOTS</t>
+  </si>
+  <si>
+    <t>100-30-350-5374-</t>
+  </si>
+  <si>
+    <t>100350</t>
+  </si>
+  <si>
+    <t>CITY OF DUNCANVILLE</t>
+  </si>
+  <si>
+    <t>Quarterly Payments for Emergency</t>
+  </si>
+  <si>
+    <t>100-30-360-5301-</t>
+  </si>
+  <si>
+    <t>Legal Services</t>
+  </si>
+  <si>
+    <t>100360</t>
+  </si>
+  <si>
+    <t>5301</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>NICHOLS, JACKSON, DILLARD HAG</t>
+  </si>
+  <si>
+    <t>PROSECUTOR LEGAL FEES; SERVICE PE</t>
+  </si>
+  <si>
+    <t>100-30-360-5374-</t>
+  </si>
+  <si>
+    <t>GREGG ANDREW SHALAN</t>
+  </si>
+  <si>
+    <t>JUDICIAL SERVICES FOR FY26 - JUDG</t>
+  </si>
+  <si>
+    <t>100-30-370-5374-</t>
+  </si>
+  <si>
+    <t>100370</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>WARREN, PERIN</t>
+  </si>
+  <si>
+    <t>Health inspections for food estab</t>
+  </si>
+  <si>
+    <t>100-10-195-5201-</t>
   </si>
   <si>
     <t>Maint - Buildings/Facilities</t>
   </si>
   <si>
+    <t>100195</t>
+  </si>
+  <si>
     <t>5201</t>
   </si>
   <si>
-    <t>BAR NONE COATINGS LLC</t>
-  </si>
-  <si>
-    <t>PREMIUM FLAKE FLOORING W/HIGH WEA</t>
-  </si>
-  <si>
-    <t>100-30-340-5204-</t>
-  </si>
-  <si>
-    <t>Maint - Automobiles</t>
-  </si>
-  <si>
-    <t>5204</t>
-  </si>
-  <si>
-    <t>SIDDONS-MARTIN EMERGENCY GROU</t>
-  </si>
-  <si>
-    <t>FY26 VEHICLE MAINTENANCE  HGAC FS</t>
-  </si>
-  <si>
-    <t>100-30-340-5374-</t>
-  </si>
-  <si>
-    <t>Special Services</t>
-  </si>
-  <si>
-    <t>5374</t>
-  </si>
-  <si>
-    <t>FRONT LINE MOBILE HEALTH, PLL</t>
-  </si>
-  <si>
-    <t>Firefighter Physicals</t>
-  </si>
-  <si>
-    <t>CITY OF DESOTO</t>
-  </si>
-  <si>
-    <t>Full Time Annual Salary</t>
-  </si>
-  <si>
-    <t>Uniforms</t>
-  </si>
-  <si>
-    <t>Certification Pay</t>
-  </si>
-  <si>
-    <t>Medical Benefit (HSA Medical Plan</t>
-  </si>
-  <si>
-    <t>Dental Insurance Benefit</t>
-  </si>
-  <si>
-    <t>Basic Term Life Benefit</t>
-  </si>
-  <si>
-    <t>Group Long Term Benefit</t>
-  </si>
-  <si>
-    <t>FIRE-DEX GW, LLC</t>
-  </si>
-  <si>
-    <t>Bunker Gear Cleaning &amp; Inspection</t>
-  </si>
-  <si>
-    <t>100-30-340-5616-</t>
-  </si>
-  <si>
-    <t>5616</t>
-  </si>
-  <si>
-    <t>CASCO INDUSTRIES, INC</t>
-  </si>
-  <si>
-    <t>PPE- COATS, PANTS, HELMETS, BOOTS</t>
-  </si>
-  <si>
-    <t>100-30-340-7103-</t>
-  </si>
-  <si>
-    <t>Building &amp; Improvements</t>
-  </si>
-  <si>
-    <t>7103</t>
-  </si>
-  <si>
-    <t>TEAM MECHANICAL</t>
-  </si>
-  <si>
-    <t>5-Ton Package HVAC Unit – Equipme</t>
-  </si>
-  <si>
-    <t>Installation Labor – Package Unit</t>
-  </si>
-  <si>
-    <t>100-30-350-5374-</t>
-  </si>
-  <si>
-    <t>100350</t>
-  </si>
-  <si>
-    <t>CITY OF DUNCANVILLE</t>
-  </si>
-  <si>
-    <t>Quarterly Payments for Emergency</t>
-  </si>
-  <si>
-    <t>100-30-360-5301-</t>
-  </si>
-  <si>
-    <t>Legal Services</t>
-  </si>
-  <si>
-    <t>100360</t>
-  </si>
-  <si>
-    <t>5301</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>NICHOLS, JACKSON, DILLARD HAG</t>
-  </si>
-  <si>
-    <t>PROSECUTOR LEGAL FEES; SERVICE PE</t>
-  </si>
-  <si>
-    <t>100-30-360-5374-</t>
-  </si>
-  <si>
-    <t>GREGG ANDREW SHALAN</t>
-  </si>
-  <si>
-    <t>JUDICIAL SERVICES FOR FY26 - JUDG</t>
-  </si>
-  <si>
-    <t>100-30-370-5374-</t>
-  </si>
-  <si>
-    <t>100370</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>WARREN, PERIN</t>
-  </si>
-  <si>
-    <t>Health inspections for food estab</t>
-  </si>
-  <si>
-    <t>221-30-380-5201-</t>
-  </si>
-  <si>
-    <t>221380</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Animal Shelter Fund</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>OLSON ELECTRIC SERVICE INC.</t>
-  </si>
-  <si>
-    <t>Repairing Light Pole -  Replacing</t>
-  </si>
-  <si>
-    <t>BETSY ROSS FLAG GIRLS, INC.</t>
-  </si>
-  <si>
-    <t>TX &amp; US Flags</t>
-  </si>
-  <si>
-    <t>100-10-195-5201-</t>
-  </si>
-  <si>
-    <t>100195</t>
-  </si>
-  <si>
     <t>410</t>
   </si>
   <si>
@@ -437,27 +374,15 @@
     <t>Service Calls</t>
   </si>
   <si>
-    <t>100-40-430-5205-</t>
-  </si>
-  <si>
-    <t>Maint - Equipment</t>
-  </si>
-  <si>
-    <t>5205</t>
-  </si>
-  <si>
-    <t>3000 Service Call Income: Service</t>
-  </si>
-  <si>
-    <t>3000 Service call income: Service</t>
-  </si>
-  <si>
     <t>VNA</t>
   </si>
   <si>
     <t>VNA Meals (Department Expense) PA</t>
   </si>
   <si>
+    <t>VNA Meals (Department Expense) Ad</t>
+  </si>
+  <si>
     <t>SULTAN KARRIEM</t>
   </si>
   <si>
@@ -518,12 +443,6 @@
     <t>100-40-450-5201-</t>
   </si>
   <si>
-    <t>WHIRLIX DESIGN INC</t>
-  </si>
-  <si>
-    <t>Demo of existing Bollard and repl</t>
-  </si>
-  <si>
     <t>Annual Fire Alarm and Sprinkler I</t>
   </si>
   <si>
@@ -632,10 +551,7 @@
     <t>Website Consulting</t>
   </si>
   <si>
-    <t>SUPERSTAR COLLISION LLC</t>
-  </si>
-  <si>
-    <t>Monthly billboard placement for 3</t>
+    <t>Final Amount Leftover from 2025 P</t>
   </si>
   <si>
     <t>100-70-710-5116-</t>
@@ -743,12 +659,6 @@
     <t>Purchase of Type D-Asphalt for th</t>
   </si>
   <si>
-    <t>BLADES GROUP, LLC</t>
-  </si>
-  <si>
-    <t>We are requesting $1,324 in a cha</t>
-  </si>
-  <si>
     <t>PARADIGM TRAFFIC SYSTEMS CORP</t>
   </si>
   <si>
@@ -771,9 +681,6 @@
   </si>
   <si>
     <t>Signs &amp; Signals materials - signs</t>
-  </si>
-  <si>
-    <t>105 Amp 12V Batteries for solar l</t>
   </si>
 </sst>
 </file>
@@ -1260,8 +1167,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1d92c175-ce4e-4ef3-b0b9-2ddbfa216fa7}">
-  <dimension ref="A1:Q88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{da6a45c0-89a0-41da-b189-53e3b895b05c}">
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="15.5714285714286" style="3" customWidth="1"/>
@@ -1280,7 +1187,7 @@
     <col min="14" max="14" width="10.7142857142857" style="7" customWidth="1"/>
     <col min="15" max="15" width="14.8571428571429" style="9" customWidth="1"/>
     <col min="16" max="16" width="12.4285714285714" style="9" customWidth="1"/>
-    <col min="17" max="17" width="33.1428571428571" style="3" customWidth="1"/>
+    <col min="17" max="17" width="31.8571428571429" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12.75">
@@ -1436,7 +1343,7 @@
         <v>100000</v>
       </c>
       <c r="P3" s="9">
-        <v>25217.33</v>
+        <v>22402.55</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -1648,7 +1555,7 @@
         <v>50000</v>
       </c>
       <c r="P7" s="9">
-        <v>12656.41</v>
+        <v>8558.04</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>41</v>
@@ -1656,16 +1563,16 @@
     </row>
     <row r="8" spans="1:17" ht="12.75">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>21</v>
@@ -1677,7 +1584,7 @@
         <v>23</v>
       </c>
       <c r="H8" s="5">
-        <v>2620429</v>
+        <v>2620179</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>24</v>
@@ -1689,36 +1596,36 @@
         <v>1</v>
       </c>
       <c r="L8" s="5">
-        <v>3972</v>
+        <v>1661</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N8" s="7">
-        <v>46149</v>
+        <v>45964</v>
       </c>
       <c r="O8" s="9">
-        <v>15000</v>
+        <v>186000</v>
       </c>
       <c r="P8" s="9">
-        <v>688.05</v>
+        <v>93132.64</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="12.75">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>21</v>
@@ -1730,7 +1637,7 @@
         <v>23</v>
       </c>
       <c r="H9" s="5">
-        <v>2620514</v>
+        <v>2620309</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>24</v>
@@ -1742,36 +1649,36 @@
         <v>1</v>
       </c>
       <c r="L9" s="5">
-        <v>5231</v>
+        <v>1012</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N9" s="7">
-        <v>46244</v>
+        <v>46043</v>
       </c>
       <c r="O9" s="9">
-        <v>32300</v>
+        <v>20819.66</v>
       </c>
       <c r="P9" s="9">
-        <v>32300</v>
+        <v>3036.44</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="12.75">
       <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>21</v>
@@ -1783,7 +1690,7 @@
         <v>23</v>
       </c>
       <c r="H10" s="5">
-        <v>2620179</v>
+        <v>2620309</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>24</v>
@@ -1792,22 +1699,22 @@
         <v>25</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5">
-        <v>1661</v>
+        <v>1012</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N10" s="7">
-        <v>45964</v>
+        <v>46043</v>
       </c>
       <c r="O10" s="9">
-        <v>186000</v>
+        <v>2633.96</v>
       </c>
       <c r="P10" s="9">
-        <v>93132.64</v>
+        <v>658.49</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>52</v>
@@ -1815,16 +1722,16 @@
     </row>
     <row r="11" spans="1:17" ht="12.75">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>21</v>
@@ -1836,7 +1743,7 @@
         <v>23</v>
       </c>
       <c r="H11" s="5">
-        <v>2620218</v>
+        <v>2620309</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>24</v>
@@ -1845,39 +1752,39 @@
         <v>25</v>
       </c>
       <c r="K11" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="5">
-        <v>4881</v>
+        <v>1012</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="N11" s="7">
-        <v>45981</v>
+        <v>46043</v>
       </c>
       <c r="O11" s="9">
-        <v>72150</v>
+        <v>250</v>
       </c>
       <c r="P11" s="9">
-        <v>625</v>
+        <v>62.50</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="12.75">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>21</v>
@@ -1898,39 +1805,39 @@
         <v>25</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5">
         <v>1012</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N12" s="7">
         <v>46043</v>
       </c>
       <c r="O12" s="9">
-        <v>20819.66</v>
+        <v>734.24</v>
       </c>
       <c r="P12" s="9">
-        <v>3036.44</v>
+        <v>183.56</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="12.75">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>21</v>
@@ -1951,39 +1858,39 @@
         <v>25</v>
       </c>
       <c r="K13" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5">
         <v>1012</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N13" s="7">
         <v>46043</v>
       </c>
       <c r="O13" s="9">
-        <v>2633.96</v>
+        <v>32.98</v>
       </c>
       <c r="P13" s="9">
-        <v>658.49</v>
+        <v>8.33</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="12.75">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>21</v>
@@ -2004,39 +1911,39 @@
         <v>25</v>
       </c>
       <c r="K14" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" s="5">
         <v>1012</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N14" s="7">
         <v>46043</v>
       </c>
       <c r="O14" s="9">
-        <v>250</v>
+        <v>14.40</v>
       </c>
       <c r="P14" s="9">
-        <v>62.50</v>
+        <v>3.54</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="12.75">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>21</v>
@@ -2057,39 +1964,39 @@
         <v>25</v>
       </c>
       <c r="K15" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L15" s="5">
         <v>1012</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N15" s="7">
         <v>46043</v>
       </c>
       <c r="O15" s="9">
-        <v>734.24</v>
+        <v>15.04</v>
       </c>
       <c r="P15" s="9">
-        <v>183.56</v>
+        <v>3.76</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="12.75">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>21</v>
@@ -2101,7 +2008,7 @@
         <v>23</v>
       </c>
       <c r="H16" s="5">
-        <v>2620309</v>
+        <v>2620385</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>24</v>
@@ -2110,39 +2017,39 @@
         <v>25</v>
       </c>
       <c r="K16" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>1012</v>
+        <v>4757</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>58</v>
       </c>
       <c r="N16" s="7">
-        <v>46043</v>
+        <v>46104</v>
       </c>
       <c r="O16" s="9">
-        <v>32.98</v>
+        <v>20000</v>
       </c>
       <c r="P16" s="9">
-        <v>8.33</v>
+        <v>361.46</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="12.75">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>21</v>
@@ -2154,7 +2061,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="5">
-        <v>2620309</v>
+        <v>2620155</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>24</v>
@@ -2163,39 +2070,39 @@
         <v>25</v>
       </c>
       <c r="K17" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5">
-        <v>1012</v>
+        <v>1056</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N17" s="7">
-        <v>46043</v>
+        <v>45951</v>
       </c>
       <c r="O17" s="9">
-        <v>14.40</v>
+        <v>65000</v>
       </c>
       <c r="P17" s="9">
-        <v>3.54</v>
+        <v>527.75</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="12.75">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>21</v>
@@ -2207,7 +2114,7 @@
         <v>23</v>
       </c>
       <c r="H18" s="5">
-        <v>2620309</v>
+        <v>2620072</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>24</v>
@@ -2216,39 +2123,39 @@
         <v>25</v>
       </c>
       <c r="K18" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L18" s="5">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N18" s="7">
-        <v>46043</v>
+        <v>45937</v>
       </c>
       <c r="O18" s="9">
-        <v>15.04</v>
+        <v>68708.51</v>
       </c>
       <c r="P18" s="9">
-        <v>3.76</v>
+        <v>21678.57</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="12.75">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>21</v>
@@ -2260,48 +2167,48 @@
         <v>23</v>
       </c>
       <c r="H19" s="5">
-        <v>2620385</v>
+        <v>2620149</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="K19" s="5">
         <v>1</v>
       </c>
       <c r="L19" s="5">
-        <v>4757</v>
+        <v>1252</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="N19" s="7">
-        <v>46104</v>
+        <v>45947</v>
       </c>
       <c r="O19" s="9">
-        <v>20000</v>
+        <v>54000</v>
       </c>
       <c r="P19" s="9">
-        <v>446.13</v>
+        <v>13978.23</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="12.75">
       <c r="A20" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>21</v>
@@ -2313,48 +2220,48 @@
         <v>23</v>
       </c>
       <c r="H20" s="5">
-        <v>2620155</v>
+        <v>2620151</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="K20" s="5">
         <v>1</v>
       </c>
       <c r="L20" s="5">
-        <v>1056</v>
+        <v>4034</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N20" s="7">
-        <v>45951</v>
+        <v>45947</v>
       </c>
       <c r="O20" s="9">
-        <v>65000</v>
+        <v>40000</v>
       </c>
       <c r="P20" s="9">
-        <v>2118.74</v>
+        <v>3333.37</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="12.75">
       <c r="A21" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>21</v>
@@ -2366,48 +2273,48 @@
         <v>23</v>
       </c>
       <c r="H21" s="5">
-        <v>2620524</v>
+        <v>2620135</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="K21" s="5">
         <v>1</v>
       </c>
       <c r="L21" s="5">
-        <v>1904</v>
+        <v>1238</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N21" s="7">
-        <v>46261</v>
+        <v>45947</v>
       </c>
       <c r="O21" s="9">
-        <v>17300</v>
+        <v>54000</v>
       </c>
       <c r="P21" s="9">
-        <v>17300</v>
+        <v>23520</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="12.75">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
@@ -2419,48 +2326,48 @@
         <v>23</v>
       </c>
       <c r="H22" s="5">
-        <v>2620524</v>
+        <v>2620370</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="K22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="5">
-        <v>1904</v>
+        <v>2214</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="N22" s="7">
-        <v>46261</v>
+        <v>46097</v>
       </c>
       <c r="O22" s="9">
-        <v>8500</v>
+        <v>10560</v>
       </c>
       <c r="P22" s="9">
-        <v>8500</v>
+        <v>2795.04</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="12.75">
       <c r="A23" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>21</v>
@@ -2472,48 +2379,48 @@
         <v>23</v>
       </c>
       <c r="H23" s="5">
-        <v>2620072</v>
+        <v>2620162</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="K23" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5">
-        <v>1020</v>
+        <v>1868</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="N23" s="7">
-        <v>45937</v>
+        <v>45953</v>
       </c>
       <c r="O23" s="9">
-        <v>68708.51</v>
+        <v>33935.65</v>
       </c>
       <c r="P23" s="9">
-        <v>21678.57</v>
+        <v>19071.76</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="12.75">
       <c r="A24" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>21</v>
@@ -2525,48 +2432,48 @@
         <v>23</v>
       </c>
       <c r="H24" s="5">
-        <v>2620149</v>
+        <v>2620162</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="5">
-        <v>1252</v>
+        <v>1868</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N24" s="7">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="O24" s="9">
-        <v>54000</v>
+        <v>18453.49</v>
       </c>
       <c r="P24" s="9">
-        <v>18619.28</v>
+        <v>18453.49</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="12.75">
       <c r="A25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>21</v>
@@ -2578,48 +2485,48 @@
         <v>23</v>
       </c>
       <c r="H25" s="5">
-        <v>2620151</v>
+        <v>2620162</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5">
-        <v>4034</v>
+        <v>1868</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N25" s="7">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="O25" s="9">
-        <v>40000</v>
+        <v>10116.86</v>
       </c>
       <c r="P25" s="9">
-        <v>3333.37</v>
+        <v>8397.66</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="12.75">
       <c r="A26" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>21</v>
@@ -2631,84 +2538,84 @@
         <v>23</v>
       </c>
       <c r="H26" s="5">
-        <v>2620135</v>
+        <v>2620040</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K26" s="5">
         <v>1</v>
       </c>
       <c r="L26" s="5">
-        <v>1238</v>
+        <v>3836</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N26" s="7">
-        <v>45947</v>
+        <v>45931</v>
       </c>
       <c r="O26" s="9">
-        <v>54000</v>
+        <v>83500</v>
       </c>
       <c r="P26" s="9">
-        <v>23520</v>
+        <v>0.04</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="12.75">
       <c r="A27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="H27" s="5">
-        <v>2620342</v>
+        <v>2620407</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="K27" s="5">
         <v>1</v>
       </c>
       <c r="L27" s="5">
-        <v>1987</v>
+        <v>1632</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>102</v>
       </c>
       <c r="N27" s="7">
-        <v>46069</v>
+        <v>46129</v>
       </c>
       <c r="O27" s="9">
-        <v>3161.92</v>
+        <v>1620</v>
       </c>
       <c r="P27" s="9">
-        <v>3161.92</v>
+        <v>1620</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>103</v>
@@ -2716,69 +2623,69 @@
     </row>
     <row r="28" spans="1:17" ht="12.75">
       <c r="A28" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="H28" s="5">
-        <v>2620389</v>
+        <v>2620407</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="K28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5">
-        <v>1402</v>
+        <v>1632</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N28" s="7">
-        <v>46111</v>
+        <v>46129</v>
       </c>
       <c r="O28" s="9">
-        <v>555.80</v>
+        <v>400</v>
       </c>
       <c r="P28" s="9">
-        <v>555.80</v>
+        <v>400</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="12.75">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>21</v>
@@ -2790,48 +2697,48 @@
         <v>23</v>
       </c>
       <c r="H29" s="5">
-        <v>2620370</v>
+        <v>2620407</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K29" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="5">
-        <v>2214</v>
+        <v>1632</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N29" s="7">
-        <v>46097</v>
+        <v>46129</v>
       </c>
       <c r="O29" s="9">
-        <v>10560</v>
+        <v>2042.50</v>
       </c>
       <c r="P29" s="9">
-        <v>2795.04</v>
+        <v>2042.50</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="12.75">
       <c r="A30" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>21</v>
@@ -2843,48 +2750,48 @@
         <v>23</v>
       </c>
       <c r="H30" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K30" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L30" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="N30" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O30" s="9">
-        <v>33935.65</v>
+        <v>150</v>
       </c>
       <c r="P30" s="9">
-        <v>19071.76</v>
+        <v>150</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="12.75">
       <c r="A31" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>21</v>
@@ -2896,48 +2803,48 @@
         <v>23</v>
       </c>
       <c r="H31" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K31" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="N31" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O31" s="9">
-        <v>18453.49</v>
+        <v>600</v>
       </c>
       <c r="P31" s="9">
-        <v>18453.49</v>
+        <v>600</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="12.75">
       <c r="A32" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>21</v>
@@ -2949,101 +2856,101 @@
         <v>23</v>
       </c>
       <c r="H32" s="5">
-        <v>2620162</v>
+        <v>2620407</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K32" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32" s="5">
-        <v>1868</v>
+        <v>1632</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="N32" s="7">
-        <v>45953</v>
+        <v>46129</v>
       </c>
       <c r="O32" s="9">
-        <v>10116.86</v>
+        <v>600</v>
       </c>
       <c r="P32" s="9">
-        <v>8397.66</v>
+        <v>600</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="12.75">
       <c r="A33" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="H33" s="5">
-        <v>2620040</v>
+        <v>2620263</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K33" s="5">
         <v>1</v>
       </c>
       <c r="L33" s="5">
-        <v>3836</v>
+        <v>1136</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="N33" s="7">
-        <v>45931</v>
+        <v>46002</v>
       </c>
       <c r="O33" s="9">
-        <v>83500</v>
+        <v>134953.54</v>
       </c>
       <c r="P33" s="9">
-        <v>0.04</v>
+        <v>30491.78</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="12.75">
       <c r="A34" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>21</v>
@@ -3055,48 +2962,48 @@
         <v>23</v>
       </c>
       <c r="H34" s="5">
-        <v>2620407</v>
+        <v>2620167</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K34" s="5">
         <v>1</v>
       </c>
       <c r="L34" s="5">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N34" s="7">
-        <v>46129</v>
+        <v>45954</v>
       </c>
       <c r="O34" s="9">
-        <v>1620</v>
+        <v>23400</v>
       </c>
       <c r="P34" s="9">
-        <v>1620</v>
+        <v>225</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75">
       <c r="A35" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>21</v>
@@ -3108,48 +3015,48 @@
         <v>23</v>
       </c>
       <c r="H35" s="5">
-        <v>2620407</v>
+        <v>2620167</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K35" s="5">
         <v>2</v>
       </c>
       <c r="L35" s="5">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N35" s="7">
-        <v>46129</v>
+        <v>45954</v>
       </c>
       <c r="O35" s="9">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="P35" s="9">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.75">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>21</v>
@@ -3161,48 +3068,48 @@
         <v>23</v>
       </c>
       <c r="H36" s="5">
-        <v>2620407</v>
+        <v>2620167</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K36" s="5">
         <v>3</v>
       </c>
       <c r="L36" s="5">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N36" s="7">
-        <v>46129</v>
+        <v>45954</v>
       </c>
       <c r="O36" s="9">
-        <v>2042.50</v>
+        <v>375</v>
       </c>
       <c r="P36" s="9">
-        <v>2042.50</v>
+        <v>75</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75">
       <c r="A37" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>21</v>
@@ -3214,366 +3121,366 @@
         <v>23</v>
       </c>
       <c r="H37" s="5">
-        <v>2620407</v>
+        <v>2620167</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K37" s="5">
         <v>4</v>
       </c>
       <c r="L37" s="5">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N37" s="7">
-        <v>46129</v>
+        <v>45954</v>
       </c>
       <c r="O37" s="9">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="P37" s="9">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="12.75">
       <c r="A38" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2620382</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K38" s="5">
+        <v>2</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2968</v>
+      </c>
+      <c r="M38" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="N38" s="7">
+        <v>46101</v>
+      </c>
+      <c r="O38" s="9">
+        <v>10000</v>
+      </c>
+      <c r="P38" s="9">
+        <v>928.96</v>
+      </c>
+      <c r="Q38" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="5">
-        <v>2620407</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K38" s="5">
-        <v>5</v>
-      </c>
-      <c r="L38" s="5">
-        <v>1632</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N38" s="7">
-        <v>46129</v>
-      </c>
-      <c r="O38" s="9">
-        <v>600</v>
-      </c>
-      <c r="P38" s="9">
-        <v>600</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="12.75">
       <c r="A39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="5">
+        <v>2620382</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K39" s="5">
+        <v>3</v>
+      </c>
+      <c r="L39" s="5">
+        <v>2968</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="5">
-        <v>2620407</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K39" s="5">
-        <v>6</v>
-      </c>
-      <c r="L39" s="5">
-        <v>1632</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="N39" s="7">
-        <v>46129</v>
+        <v>46101</v>
       </c>
       <c r="O39" s="9">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="P39" s="9">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="12.75">
       <c r="A40" s="3" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="H40" s="5">
-        <v>2620263</v>
+        <v>2620388</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K40" s="5">
         <v>1</v>
       </c>
       <c r="L40" s="5">
-        <v>1136</v>
+        <v>5125</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N40" s="7">
-        <v>46002</v>
+        <v>46107</v>
       </c>
       <c r="O40" s="9">
-        <v>134953.54</v>
+        <v>5250</v>
       </c>
       <c r="P40" s="9">
-        <v>30491.78</v>
+        <v>1312.50</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="12.75">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="H41" s="5">
-        <v>2620167</v>
+        <v>2620382</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="K41" s="5">
         <v>1</v>
       </c>
       <c r="L41" s="5">
-        <v>1620</v>
+        <v>2968</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="N41" s="7">
-        <v>45954</v>
+        <v>46101</v>
       </c>
       <c r="O41" s="9">
-        <v>23400</v>
+        <v>18000</v>
       </c>
       <c r="P41" s="9">
-        <v>225</v>
+        <v>4010.58</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="12.75">
       <c r="A42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="5">
+        <v>2620089</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K42" s="5">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5">
+        <v>1206</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N42" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O42" s="9">
+        <v>2755.20</v>
+      </c>
+      <c r="P42" s="9">
+        <v>495.58</v>
+      </c>
+      <c r="Q42" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K42" s="5">
-        <v>2</v>
-      </c>
-      <c r="L42" s="5">
-        <v>1620</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N42" s="7">
-        <v>45954</v>
-      </c>
-      <c r="O42" s="9">
-        <v>250</v>
-      </c>
-      <c r="P42" s="9">
-        <v>250</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="12.75">
       <c r="A43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2620089</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K43" s="5">
+        <v>2</v>
+      </c>
+      <c r="L43" s="5">
+        <v>1206</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N43" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O43" s="9">
+        <v>9360</v>
+      </c>
+      <c r="P43" s="9">
+        <v>2966.03</v>
+      </c>
+      <c r="Q43" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K43" s="5">
-        <v>3</v>
-      </c>
-      <c r="L43" s="5">
-        <v>1620</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N43" s="7">
-        <v>45954</v>
-      </c>
-      <c r="O43" s="9">
-        <v>375</v>
-      </c>
-      <c r="P43" s="9">
-        <v>75</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="12.75">
       <c r="A44" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>21</v>
@@ -3585,48 +3492,48 @@
         <v>23</v>
       </c>
       <c r="H44" s="5">
-        <v>2620167</v>
+        <v>2620094</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K44" s="5">
+        <v>1</v>
+      </c>
+      <c r="L44" s="5">
+        <v>1049</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K44" s="5">
-        <v>4</v>
-      </c>
-      <c r="L44" s="5">
-        <v>1620</v>
-      </c>
-      <c r="M44" s="3" t="s">
+      <c r="N44" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O44" s="9">
+        <v>25000</v>
+      </c>
+      <c r="P44" s="9">
+        <v>11965.59</v>
+      </c>
+      <c r="Q44" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="N44" s="7">
-        <v>45954</v>
-      </c>
-      <c r="O44" s="9">
-        <v>500</v>
-      </c>
-      <c r="P44" s="9">
-        <v>500</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="12.75">
       <c r="A45" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>21</v>
@@ -3638,48 +3545,48 @@
         <v>23</v>
       </c>
       <c r="H45" s="5">
-        <v>2620392</v>
+        <v>2620095</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K45" s="5">
         <v>1</v>
       </c>
       <c r="L45" s="5">
-        <v>1620</v>
+        <v>1974</v>
       </c>
       <c r="M45" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N45" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O45" s="9">
+        <v>35000</v>
+      </c>
+      <c r="P45" s="9">
+        <v>655.06</v>
+      </c>
+      <c r="Q45" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="N45" s="7">
-        <v>46111</v>
-      </c>
-      <c r="O45" s="9">
-        <v>8690</v>
-      </c>
-      <c r="P45" s="9">
-        <v>8690</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="12.75">
       <c r="A46" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>21</v>
@@ -3691,48 +3598,48 @@
         <v>23</v>
       </c>
       <c r="H46" s="5">
-        <v>2620392</v>
+        <v>2620148</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K46" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="5">
-        <v>1620</v>
+        <v>1689</v>
       </c>
       <c r="M46" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N46" s="7">
+        <v>45947</v>
+      </c>
+      <c r="O46" s="9">
+        <v>39434</v>
+      </c>
+      <c r="P46" s="9">
+        <v>36.84</v>
+      </c>
+      <c r="Q46" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="N46" s="7">
-        <v>46111</v>
-      </c>
-      <c r="O46" s="9">
-        <v>400</v>
-      </c>
-      <c r="P46" s="9">
-        <v>400</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="12.75">
       <c r="A47" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>21</v>
@@ -3744,48 +3651,48 @@
         <v>23</v>
       </c>
       <c r="H47" s="5">
-        <v>2620382</v>
+        <v>2620158</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K47" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="5">
-        <v>2968</v>
+        <v>1464</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="N47" s="7">
-        <v>46101</v>
+        <v>45952</v>
       </c>
       <c r="O47" s="9">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="P47" s="9">
-        <v>928.96</v>
+        <v>2010.92</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="12.75">
       <c r="A48" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>21</v>
@@ -3797,101 +3704,101 @@
         <v>23</v>
       </c>
       <c r="H48" s="5">
-        <v>2620388</v>
+        <v>2620159</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K48" s="5">
         <v>1</v>
       </c>
       <c r="L48" s="5">
-        <v>5125</v>
+        <v>1464</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="N48" s="7">
-        <v>46107</v>
+        <v>45952</v>
       </c>
       <c r="O48" s="9">
-        <v>5250</v>
+        <v>75000</v>
       </c>
       <c r="P48" s="9">
-        <v>1312.50</v>
+        <v>8032.32</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="12.75">
       <c r="A49" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="H49" s="5">
-        <v>2620382</v>
+        <v>2620147</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K49" s="5">
         <v>1</v>
       </c>
       <c r="L49" s="5">
-        <v>2968</v>
+        <v>2214</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="N49" s="7">
-        <v>46101</v>
+        <v>45947</v>
       </c>
       <c r="O49" s="9">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="P49" s="9">
-        <v>4010.58</v>
+        <v>438.69</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="12.75">
       <c r="A50" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>21</v>
@@ -3903,48 +3810,48 @@
         <v>23</v>
       </c>
       <c r="H50" s="5">
-        <v>2620089</v>
+        <v>2620249</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K50" s="5">
         <v>1</v>
       </c>
       <c r="L50" s="5">
-        <v>1206</v>
+        <v>4921</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="N50" s="7">
-        <v>45943</v>
+        <v>45999</v>
       </c>
       <c r="O50" s="9">
-        <v>2755.20</v>
+        <v>13400</v>
       </c>
       <c r="P50" s="9">
-        <v>495.58</v>
+        <v>1845.67</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="12.75">
       <c r="A51" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>21</v>
@@ -3956,48 +3863,48 @@
         <v>23</v>
       </c>
       <c r="H51" s="5">
-        <v>2620089</v>
+        <v>2620379</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K51" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="5">
-        <v>1206</v>
+        <v>2214</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="N51" s="7">
-        <v>45943</v>
+        <v>46098</v>
       </c>
       <c r="O51" s="9">
-        <v>9360</v>
+        <v>600</v>
       </c>
       <c r="P51" s="9">
-        <v>2966.03</v>
+        <v>276.46</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="12.75">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>21</v>
@@ -4009,48 +3916,48 @@
         <v>23</v>
       </c>
       <c r="H52" s="5">
-        <v>2620094</v>
+        <v>2620379</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K52" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="5">
-        <v>1049</v>
+        <v>2214</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="N52" s="7">
-        <v>45943</v>
+        <v>46098</v>
       </c>
       <c r="O52" s="9">
-        <v>25000</v>
+        <v>2476</v>
       </c>
       <c r="P52" s="9">
-        <v>12285.53</v>
+        <v>809.80</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="12.75">
       <c r="A53" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>21</v>
@@ -4062,48 +3969,48 @@
         <v>23</v>
       </c>
       <c r="H53" s="5">
-        <v>2620095</v>
+        <v>2620379</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K53" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="5">
-        <v>1974</v>
+        <v>2214</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="N53" s="7">
-        <v>45943</v>
+        <v>46098</v>
       </c>
       <c r="O53" s="9">
-        <v>35000</v>
+        <v>788.13</v>
       </c>
       <c r="P53" s="9">
-        <v>671.58</v>
+        <v>314.12</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="12.75">
       <c r="A54" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>21</v>
@@ -4115,48 +4022,48 @@
         <v>23</v>
       </c>
       <c r="H54" s="5">
-        <v>2620148</v>
+        <v>2620090</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K54" s="5">
         <v>1</v>
       </c>
       <c r="L54" s="5">
-        <v>1689</v>
+        <v>2018</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="N54" s="7">
-        <v>45947</v>
+        <v>45943</v>
       </c>
       <c r="O54" s="9">
-        <v>38734</v>
+        <v>9100</v>
       </c>
       <c r="P54" s="9">
-        <v>37.79</v>
+        <v>87.50</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="12.75">
       <c r="A55" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>21</v>
@@ -4168,34 +4075,34 @@
         <v>23</v>
       </c>
       <c r="H55" s="5">
-        <v>2620158</v>
+        <v>2620146</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="K55" s="5">
         <v>1</v>
       </c>
       <c r="L55" s="5">
-        <v>1464</v>
+        <v>4767</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="N55" s="7">
-        <v>45952</v>
+        <v>45947</v>
       </c>
       <c r="O55" s="9">
-        <v>8000</v>
+        <v>3600</v>
       </c>
       <c r="P55" s="9">
-        <v>2499.23</v>
+        <v>2550</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="12.75">
@@ -4203,473 +4110,473 @@
         <v>152</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="5">
+        <v>2620255</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="5">
-        <v>2620159</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="K56" s="5">
         <v>1</v>
       </c>
       <c r="L56" s="5">
-        <v>1464</v>
+        <v>2147</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N56" s="7">
-        <v>45952</v>
+        <v>46000</v>
       </c>
       <c r="O56" s="9">
-        <v>75000</v>
+        <v>30000</v>
       </c>
       <c r="P56" s="9">
-        <v>8032.32</v>
+        <v>7500</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="12.75">
       <c r="A57" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H57" s="5">
-        <v>2620093</v>
+        <v>2620295</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="K57" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L57" s="5">
-        <v>2106</v>
+        <v>3985</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N57" s="7">
-        <v>45943</v>
+        <v>46030</v>
       </c>
       <c r="O57" s="9">
-        <v>3364.55</v>
+        <v>10000</v>
       </c>
       <c r="P57" s="9">
-        <v>0.01</v>
+        <v>2611.86</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="12.75">
       <c r="A58" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H58" s="5">
+        <v>2620295</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K58" s="5">
+        <v>7</v>
+      </c>
+      <c r="L58" s="5">
+        <v>3985</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N58" s="7">
+        <v>46030</v>
+      </c>
+      <c r="O58" s="9">
+        <v>21000</v>
+      </c>
+      <c r="P58" s="9">
+        <v>8291.88</v>
+      </c>
+      <c r="Q58" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H58" s="5">
-        <v>2620147</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K58" s="5">
-        <v>1</v>
-      </c>
-      <c r="L58" s="5">
-        <v>2214</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="N58" s="7">
-        <v>45947</v>
-      </c>
-      <c r="O58" s="9">
-        <v>4000</v>
-      </c>
-      <c r="P58" s="9">
-        <v>438.69</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="12.75">
       <c r="A59" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H59" s="5">
-        <v>2620249</v>
+        <v>2620097</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="5">
-        <v>4921</v>
+        <v>1893</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N59" s="7">
-        <v>45999</v>
+        <v>45943</v>
       </c>
       <c r="O59" s="9">
-        <v>13400</v>
+        <v>16104</v>
       </c>
       <c r="P59" s="9">
-        <v>1845.67</v>
+        <v>237</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="12.75">
       <c r="A60" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H60" s="5">
-        <v>2620379</v>
+        <v>2620098</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K60" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5">
-        <v>2214</v>
+        <v>1227</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="N60" s="7">
-        <v>46098</v>
+        <v>45943</v>
       </c>
       <c r="O60" s="9">
-        <v>600</v>
+        <v>18082.30</v>
       </c>
       <c r="P60" s="9">
-        <v>276.46</v>
+        <v>4285.45</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="12.75">
       <c r="A61" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H61" s="5">
-        <v>2620379</v>
+        <v>2620327</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K61" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="5">
-        <v>2214</v>
+        <v>1650</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="N61" s="7">
-        <v>46098</v>
+        <v>46057</v>
       </c>
       <c r="O61" s="9">
-        <v>2476</v>
+        <v>12000</v>
       </c>
       <c r="P61" s="9">
-        <v>2476</v>
+        <v>5700</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="12.75">
       <c r="A62" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H62" s="5">
-        <v>2620379</v>
+        <v>2620327</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K62" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" s="5">
-        <v>2214</v>
+        <v>1650</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="N62" s="7">
-        <v>46098</v>
+        <v>46057</v>
       </c>
       <c r="O62" s="9">
-        <v>788.13</v>
+        <v>6900</v>
       </c>
       <c r="P62" s="9">
-        <v>314.12</v>
+        <v>600</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="12.75">
       <c r="A63" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H63" s="5">
-        <v>2620090</v>
+        <v>2620104</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K63" s="5">
         <v>1</v>
       </c>
       <c r="L63" s="5">
-        <v>2018</v>
+        <v>3600</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N63" s="7">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="O63" s="9">
-        <v>9100</v>
+        <v>20556.12</v>
       </c>
       <c r="P63" s="9">
-        <v>87.50</v>
+        <v>1713.13</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="12.75">
       <c r="A64" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="H64" s="5">
-        <v>2620146</v>
+        <v>2620280</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K64" s="5">
         <v>1</v>
       </c>
       <c r="L64" s="5">
-        <v>4767</v>
+        <v>3985</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="N64" s="7">
-        <v>45947</v>
+        <v>46014</v>
       </c>
       <c r="O64" s="9">
-        <v>3600</v>
+        <v>5374.10</v>
       </c>
       <c r="P64" s="9">
-        <v>2550</v>
+        <v>603.50</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>178</v>
@@ -4680,13 +4587,13 @@
         <v>179</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>21</v>
@@ -4698,1253 +4605,670 @@
         <v>23</v>
       </c>
       <c r="H65" s="5">
-        <v>2620255</v>
+        <v>2620051</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K65" s="5">
         <v>1</v>
       </c>
       <c r="L65" s="5">
-        <v>2147</v>
+        <v>4906</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N65" s="7">
-        <v>46000</v>
+        <v>45933</v>
       </c>
       <c r="O65" s="9">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="P65" s="9">
-        <v>7500</v>
+        <v>2041.33</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="12.75">
       <c r="A66" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="5">
+        <v>2620152</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K66" s="5">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5">
+        <v>1954</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="N66" s="7">
+        <v>45950</v>
+      </c>
+      <c r="O66" s="9">
+        <v>40000</v>
+      </c>
+      <c r="P66" s="9">
+        <v>12252.50</v>
+      </c>
+      <c r="Q66" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H66" s="5">
-        <v>2620295</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K66" s="5">
-        <v>5</v>
-      </c>
-      <c r="L66" s="5">
-        <v>3985</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="N66" s="7">
-        <v>46030</v>
-      </c>
-      <c r="O66" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P66" s="9">
-        <v>2611.86</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="12.75">
       <c r="A67" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="5">
+        <v>2620284</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K67" s="5">
+        <v>4</v>
+      </c>
+      <c r="L67" s="5">
+        <v>3099</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="N67" s="7">
+        <v>46028</v>
+      </c>
+      <c r="O67" s="9">
+        <v>17210.50</v>
+      </c>
+      <c r="P67" s="9">
+        <v>1357.75</v>
+      </c>
+      <c r="Q67" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="H67" s="5">
-        <v>2620295</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K67" s="5">
-        <v>7</v>
-      </c>
-      <c r="L67" s="5">
-        <v>3985</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="N67" s="7">
-        <v>46030</v>
-      </c>
-      <c r="O67" s="9">
-        <v>21000</v>
-      </c>
-      <c r="P67" s="9">
-        <v>8291.88</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="12.75">
       <c r="A68" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H68" s="5">
-        <v>2620097</v>
+        <v>2620022</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="K68" s="5">
         <v>2</v>
       </c>
       <c r="L68" s="5">
-        <v>1893</v>
+        <v>1062</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N68" s="7">
-        <v>45943</v>
+        <v>45925</v>
       </c>
       <c r="O68" s="9">
-        <v>16104</v>
+        <v>20000</v>
       </c>
       <c r="P68" s="9">
-        <v>237</v>
+        <v>233.61</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="12.75">
       <c r="A69" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H69" s="5">
-        <v>2620098</v>
+        <v>2620296</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="K69" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L69" s="5">
-        <v>1227</v>
+        <v>3739</v>
       </c>
       <c r="M69" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N69" s="7">
+        <v>46034</v>
+      </c>
+      <c r="O69" s="9">
+        <v>5336</v>
+      </c>
+      <c r="P69" s="9">
+        <v>1509.50</v>
+      </c>
+      <c r="Q69" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="N69" s="7">
-        <v>45943</v>
-      </c>
-      <c r="O69" s="9">
-        <v>18082.30</v>
-      </c>
-      <c r="P69" s="9">
-        <v>4285.45</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="12.75">
       <c r="A70" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H70" s="5">
-        <v>2620327</v>
+        <v>2620061</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="K70" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="5">
-        <v>1650</v>
+        <v>4918</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N70" s="7">
-        <v>46057</v>
+        <v>45933</v>
       </c>
       <c r="O70" s="9">
-        <v>12000</v>
+        <v>5963</v>
       </c>
       <c r="P70" s="9">
-        <v>5700</v>
+        <v>355</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="12.75">
       <c r="A71" s="3" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H71" s="5">
-        <v>2620327</v>
+        <v>2620050</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="K71" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L71" s="5">
-        <v>1650</v>
+        <v>1417</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="N71" s="7">
-        <v>46057</v>
+        <v>45933</v>
       </c>
       <c r="O71" s="9">
-        <v>6900</v>
+        <v>1873</v>
       </c>
       <c r="P71" s="9">
-        <v>600</v>
+        <v>27.08</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="12.75">
       <c r="A72" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H72" s="5">
-        <v>2620104</v>
+        <v>2620025</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="K72" s="5">
         <v>1</v>
       </c>
       <c r="L72" s="5">
-        <v>3600</v>
+        <v>1949</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="N72" s="7">
-        <v>45944</v>
+        <v>45925</v>
       </c>
       <c r="O72" s="9">
-        <v>20556.12</v>
+        <v>10000</v>
       </c>
       <c r="P72" s="9">
-        <v>5139.15</v>
+        <v>747</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="12.75">
       <c r="A73" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H73" s="5">
-        <v>2620493</v>
+        <v>2620027</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="K73" s="5">
         <v>1</v>
       </c>
       <c r="L73" s="5">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="N73" s="7">
-        <v>46223</v>
+        <v>45925</v>
       </c>
       <c r="O73" s="9">
-        <v>5640</v>
+        <v>30000</v>
       </c>
       <c r="P73" s="9">
-        <v>1880</v>
+        <v>127.72</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="12.75">
       <c r="A74" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="5">
+        <v>2620021</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="5">
-        <v>2620051</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="K74" s="5">
         <v>1</v>
       </c>
       <c r="L74" s="5">
-        <v>4906</v>
+        <v>1271</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N74" s="7">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="O74" s="9">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="P74" s="9">
-        <v>2041.33</v>
+        <v>5000</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="12.75">
       <c r="A75" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="5">
+        <v>2620023</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" s="5">
-        <v>2620152</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="K75" s="5">
         <v>1</v>
       </c>
       <c r="L75" s="5">
-        <v>1954</v>
+        <v>1071</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N75" s="7">
-        <v>45950</v>
+        <v>45925</v>
       </c>
       <c r="O75" s="9">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="P75" s="9">
-        <v>17112.50</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="12.75">
       <c r="A76" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="5">
+        <v>2620024</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H76" s="5">
-        <v>2620284</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L76" s="5">
-        <v>3099</v>
+        <v>1861</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N76" s="7">
-        <v>46028</v>
+        <v>45925</v>
       </c>
       <c r="O76" s="9">
-        <v>17210.50</v>
+        <v>3000</v>
       </c>
       <c r="P76" s="9">
-        <v>3112.75</v>
+        <v>107.01</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="12.75">
       <c r="A77" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="5">
+        <v>2620153</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="K77" s="5">
+        <v>1</v>
+      </c>
+      <c r="L77" s="5">
+        <v>1755</v>
+      </c>
+      <c r="M77" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H77" s="5">
-        <v>2620022</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K77" s="5">
-        <v>2</v>
-      </c>
-      <c r="L77" s="5">
-        <v>1062</v>
-      </c>
-      <c r="M77" s="3" t="s">
+      <c r="N77" s="7">
+        <v>45950</v>
+      </c>
+      <c r="O77" s="9">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="9">
+        <v>734.85</v>
+      </c>
+      <c r="Q77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="N77" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O77" s="9">
-        <v>20000</v>
-      </c>
-      <c r="P77" s="9">
-        <v>233.61</v>
-      </c>
-      <c r="Q77" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="12.75">
-      <c r="A78" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H78" s="5">
-        <v>2620296</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K78" s="5">
-        <v>2</v>
-      </c>
-      <c r="L78" s="5">
-        <v>3739</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="N78" s="7">
-        <v>46034</v>
-      </c>
-      <c r="O78" s="9">
-        <v>5336</v>
-      </c>
-      <c r="P78" s="9">
-        <v>1509.50</v>
-      </c>
-      <c r="Q78" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="12.75">
-      <c r="A79" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" s="5">
-        <v>2620061</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K79" s="5">
-        <v>2</v>
-      </c>
-      <c r="L79" s="5">
-        <v>4918</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N79" s="7">
-        <v>45933</v>
-      </c>
-      <c r="O79" s="9">
-        <v>5963</v>
-      </c>
-      <c r="P79" s="9">
-        <v>355</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="12.75">
-      <c r="A80" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80" s="5">
-        <v>2620050</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K80" s="5">
-        <v>1</v>
-      </c>
-      <c r="L80" s="5">
-        <v>1417</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="N80" s="7">
-        <v>45933</v>
-      </c>
-      <c r="O80" s="9">
-        <v>1873</v>
-      </c>
-      <c r="P80" s="9">
-        <v>27.08</v>
-      </c>
-      <c r="Q80" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="12.75">
-      <c r="A81" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" s="5">
-        <v>2620025</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K81" s="5">
-        <v>1</v>
-      </c>
-      <c r="L81" s="5">
-        <v>1949</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N81" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O81" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P81" s="9">
-        <v>747</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="12.75">
-      <c r="A82" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="5">
-        <v>2620027</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K82" s="5">
-        <v>1</v>
-      </c>
-      <c r="L82" s="5">
-        <v>1400</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="N82" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O82" s="9">
-        <v>30000</v>
-      </c>
-      <c r="P82" s="9">
-        <v>1469.83</v>
-      </c>
-      <c r="Q82" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="12.75">
-      <c r="A83" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="5">
-        <v>2620048</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K83" s="5">
-        <v>2</v>
-      </c>
-      <c r="L83" s="5">
-        <v>3867</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="N83" s="7">
-        <v>45929</v>
-      </c>
-      <c r="O83" s="9">
-        <v>6324</v>
-      </c>
-      <c r="P83" s="9">
-        <v>1302</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="12.75">
-      <c r="A84" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="5">
-        <v>2620021</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K84" s="5">
-        <v>1</v>
-      </c>
-      <c r="L84" s="5">
-        <v>1271</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="N84" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O84" s="9">
-        <v>5000</v>
-      </c>
-      <c r="P84" s="9">
-        <v>5000</v>
-      </c>
-      <c r="Q84" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="12.75">
-      <c r="A85" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="5">
-        <v>2620023</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K85" s="5">
-        <v>1</v>
-      </c>
-      <c r="L85" s="5">
-        <v>1071</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="N85" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O85" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P85" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q85" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="12.75">
-      <c r="A86" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="5">
-        <v>2620024</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K86" s="5">
-        <v>1</v>
-      </c>
-      <c r="L86" s="5">
-        <v>1861</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="N86" s="7">
-        <v>45925</v>
-      </c>
-      <c r="O86" s="9">
-        <v>3000</v>
-      </c>
-      <c r="P86" s="9">
-        <v>107.01</v>
-      </c>
-      <c r="Q86" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="12.75">
-      <c r="A87" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="5">
-        <v>2620153</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K87" s="5">
-        <v>1</v>
-      </c>
-      <c r="L87" s="5">
-        <v>1755</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="N87" s="7">
-        <v>45950</v>
-      </c>
-      <c r="O87" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P87" s="9">
-        <v>3623</v>
-      </c>
-      <c r="Q87" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="12.75">
-      <c r="A88" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="5">
-        <v>2620495</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K88" s="5">
-        <v>1</v>
-      </c>
-      <c r="L88" s="5">
-        <v>1071</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="N88" s="7">
-        <v>46223</v>
-      </c>
-      <c r="O88" s="9">
-        <v>3852</v>
-      </c>
-      <c r="P88" s="9">
-        <v>3852</v>
-      </c>
-      <c r="Q88" s="3" t="s">
-        <v>252</v>
       </c>
     </row>
   </sheetData>
